--- a/투자관련_개발현황_20250601.xlsx
+++ b/투자관련_개발현황_20250601.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MetaM\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/409b82bc37418700/바탕 화면/investment/investment_strategy/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F81ACB94-9D9E-4D70-8436-AA565A3160B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="96" documentId="13_ncr:1_{F81ACB94-9D9E-4D70-8436-AA565A3160B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4A2A849C-4BDD-47B2-BFF6-335534D2018D}"/>
   <bookViews>
-    <workbookView xWindow="2625" yWindow="-19470" windowWidth="20925" windowHeight="15345" xr2:uid="{2C5A105A-917D-4FDB-B541-D72FFAFAEB11}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="23400" activeTab="1" xr2:uid="{2C5A105A-917D-4FDB-B541-D72FFAFAEB11}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="77">
   <si>
     <t>미국주식</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -215,6 +216,116 @@
   </si>
   <si>
     <t xml:space="preserve">google drive에 저장 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>위치</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>역할</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>한국수출입데이터_수집_V2.ipynb</t>
+  </si>
+  <si>
+    <t>수출데이터 수집</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>run_trade_data_adv_forecast.py</t>
+  </si>
+  <si>
+    <t>investment\investment_strategy\Korea_Market\collection\한국수출입데이터_수집_V2.ipynb</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>investment\investment_strategy\Korea_Market\analysis\Korea_trade_data_forecast\run_trade_data_adv_forecast.py</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>수출데이터 기반으로 수출 데이터 시계열 예측</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>한국_수출품목_증가율_조회.ipynb</t>
+  </si>
+  <si>
+    <t>investment\investment_strategy\Korea_Market\analysis\한국_수출품목_증가율_조회.ipynb</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">시계열예측결과 확인 및 분석 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>주가예측</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ROA_ROE_Re 측정</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dart_korea_fs_loader_v3.ipynb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DART에서 국내 상장사 재무데이터 수집 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>data_process_ROE_ROA.ipynb</t>
+  </si>
+  <si>
+    <t>DART에서  수집된 데이터를 기반으로 상장사별 ROE, ROA, 각종 재무비율 시계열 측정</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>국내 BS, IS, Re 데이터</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>KSE_RIM_Valuation.ipynb</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">ROE,Re 를 이용해서 RIM 모형으로 주식의 value와 경제적 해자 측정 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>run_korea_psr_valuation_batch_v3.py</t>
+  </si>
+  <si>
+    <t>investment\investment_strategy\Korea_Market\collection\DART_API\dart_korea_fs_loader_v3.ipynb</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>investment\investment_strategy\Korea_Market\collection\DART_API\data_process_ROE_ROA.ipynb</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>investment\investment_strategy\Korea_Market\valuation\RIM_valuation\KSE_RIM_Valuation.ipynb</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>investment\investment_strategy\Korea_Market\valuation\kse_valuation_machine\run_korea_psr_valuation_batch_v3.py</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>매출, PSR 데이터를 기반으로 상대 valuation을 이용한 목표주가 산출 (매출을 DART DB와 연결필요)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">시가총액 데이터 수집 (일간) </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>investment\investment_strategy\Korea_Market\collection\ks_marketcap_loader.py</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ks_marketcap_loader.py</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -247,7 +358,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -341,13 +452,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -407,6 +529,24 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1125,4 +1265,4738 @@
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9CB4C0D0-ABBD-45CD-85E6-EB7927E4F500}">
+  <dimension ref="A1:XFB36"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="14.625" customWidth="1"/>
+    <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="26.5" customWidth="1"/>
+    <col min="5" max="5" width="37.625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="110.75" customWidth="1"/>
+    <col min="7" max="7" width="43.5" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2" s="2"/>
+      <c r="F2" s="4"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="17.25" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="D6" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="E6" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="F6" s="13" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E8" s="2"/>
+      <c r="F8" s="4"/>
+    </row>
+    <row r="9" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B9" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="D9" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="E9" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="F9" s="16" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B10" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="D10" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="E10" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="F10" s="19" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="17.25" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="F11" s="10" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A13" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B14" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="D14" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="E14" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="F14" s="16" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="17.25" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="D15" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="E15" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="F15" s="10" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A16" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1022 1026:2046 2050:3070 3074:4094 4098:5118 5122:6142 6146:7166 7170:8190 8194:9214 9218:10238 10242:11262 11266:12286 12290:13310 13314:14334 14338:15358 15362:16382" x14ac:dyDescent="0.3">
+      <c r="A17" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E17" s="2"/>
+      <c r="F17" s="4"/>
+    </row>
+    <row r="18" spans="1:1022 1026:2046 2050:3070 3074:4094 4098:5118 5122:6142 6146:7166 7170:8190 8194:9214 9218:10238 10242:11262 11266:12286 12290:13310 13314:14334 14338:15358 15362:16382" x14ac:dyDescent="0.3">
+      <c r="A18" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E18" s="2"/>
+      <c r="F18" s="4"/>
+    </row>
+    <row r="19" spans="1:1022 1026:2046 2050:3070 3074:4094 4098:5118 5122:6142 6146:7166 7170:8190 8194:9214 9218:10238 10242:11262 11266:12286 12290:13310 13314:14334 14338:15358 15362:16382" x14ac:dyDescent="0.3">
+      <c r="E19" s="1"/>
+      <c r="F19" s="1"/>
+    </row>
+    <row r="21" spans="1:1022 1026:2046 2050:3070 3074:4094 4098:5118 5122:6142 6146:7166 7170:8190 8194:9214 9218:10238 10242:11262 11266:12286 12290:13310 13314:14334 14338:15358 15362:16382" x14ac:dyDescent="0.3">
+      <c r="A21" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F21" s="24" t="s">
+        <v>48</v>
+      </c>
+      <c r="G21" s="24" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1022 1026:2046 2050:3070 3074:4094 4098:5118 5122:6142 6146:7166 7170:8190 8194:9214 9218:10238 10242:11262 11266:12286 12290:13310 13314:14334 14338:15358 15362:16382" x14ac:dyDescent="0.3">
+      <c r="A22" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1022 1026:2046 2050:3070 3074:4094 4098:5118 5122:6142 6146:7166 7170:8190 8194:9214 9218:10238 10242:11262 11266:12286 12290:13310 13314:14334 14338:15358 15362:16382" x14ac:dyDescent="0.3">
+      <c r="A23" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1022 1026:2046 2050:3070 3074:4094 4098:5118 5122:6142 6146:7166 7170:8190 8194:9214 9218:10238 10242:11262 11266:12286 12290:13310 13314:14334 14338:15358 15362:16382" x14ac:dyDescent="0.3">
+      <c r="A24" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1022 1026:2046 2050:3070 3074:4094 4098:5118 5122:6142 6146:7166 7170:8190 8194:9214 9218:10238 10242:11262 11266:12286 12290:13310 13314:14334 14338:15358 15362:16382" s="20" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="J25" s="21"/>
+      <c r="N25" s="21"/>
+      <c r="R25" s="21"/>
+      <c r="V25" s="21"/>
+      <c r="Z25" s="21"/>
+      <c r="AD25" s="21"/>
+      <c r="AH25" s="21"/>
+      <c r="AL25" s="21"/>
+      <c r="AP25" s="21"/>
+      <c r="AT25" s="21"/>
+      <c r="AX25" s="21"/>
+      <c r="BB25" s="21"/>
+      <c r="BF25" s="21"/>
+      <c r="BJ25" s="21"/>
+      <c r="BN25" s="21"/>
+      <c r="BR25" s="21"/>
+      <c r="BV25" s="21"/>
+      <c r="BZ25" s="21"/>
+      <c r="CD25" s="21"/>
+      <c r="CH25" s="21"/>
+      <c r="CL25" s="21"/>
+      <c r="CP25" s="21"/>
+      <c r="CT25" s="21"/>
+      <c r="CX25" s="21"/>
+      <c r="DB25" s="21"/>
+      <c r="DF25" s="21"/>
+      <c r="DJ25" s="21"/>
+      <c r="DN25" s="21"/>
+      <c r="DR25" s="21"/>
+      <c r="DV25" s="21"/>
+      <c r="DZ25" s="21"/>
+      <c r="ED25" s="21"/>
+      <c r="EH25" s="21"/>
+      <c r="EL25" s="21"/>
+      <c r="EP25" s="21"/>
+      <c r="ET25" s="21"/>
+      <c r="EX25" s="21"/>
+      <c r="FB25" s="21"/>
+      <c r="FF25" s="21"/>
+      <c r="FJ25" s="21"/>
+      <c r="FN25" s="21"/>
+      <c r="FR25" s="21"/>
+      <c r="FV25" s="21"/>
+      <c r="FZ25" s="21"/>
+      <c r="GD25" s="21"/>
+      <c r="GH25" s="21"/>
+      <c r="GL25" s="21"/>
+      <c r="GP25" s="21"/>
+      <c r="GT25" s="21"/>
+      <c r="GX25" s="21"/>
+      <c r="HB25" s="21"/>
+      <c r="HF25" s="21"/>
+      <c r="HJ25" s="21"/>
+      <c r="HN25" s="21"/>
+      <c r="HR25" s="21"/>
+      <c r="HV25" s="21"/>
+      <c r="HZ25" s="21"/>
+      <c r="ID25" s="21"/>
+      <c r="IH25" s="21"/>
+      <c r="IL25" s="21"/>
+      <c r="IP25" s="21"/>
+      <c r="IT25" s="21"/>
+      <c r="IX25" s="21"/>
+      <c r="JB25" s="21"/>
+      <c r="JF25" s="21"/>
+      <c r="JJ25" s="21"/>
+      <c r="JN25" s="21"/>
+      <c r="JR25" s="21"/>
+      <c r="JV25" s="21"/>
+      <c r="JZ25" s="21"/>
+      <c r="KD25" s="21"/>
+      <c r="KH25" s="21"/>
+      <c r="KL25" s="21"/>
+      <c r="KP25" s="21"/>
+      <c r="KT25" s="21"/>
+      <c r="KX25" s="21"/>
+      <c r="LB25" s="21"/>
+      <c r="LF25" s="21"/>
+      <c r="LJ25" s="21"/>
+      <c r="LN25" s="21"/>
+      <c r="LR25" s="21"/>
+      <c r="LV25" s="21"/>
+      <c r="LZ25" s="21"/>
+      <c r="MD25" s="21"/>
+      <c r="MH25" s="21"/>
+      <c r="ML25" s="21"/>
+      <c r="MP25" s="21"/>
+      <c r="MT25" s="21"/>
+      <c r="MX25" s="21"/>
+      <c r="NB25" s="21"/>
+      <c r="NF25" s="21"/>
+      <c r="NJ25" s="21"/>
+      <c r="NN25" s="21"/>
+      <c r="NR25" s="21"/>
+      <c r="NV25" s="21"/>
+      <c r="NZ25" s="21"/>
+      <c r="OD25" s="21"/>
+      <c r="OH25" s="21"/>
+      <c r="OL25" s="21"/>
+      <c r="OP25" s="21"/>
+      <c r="OT25" s="21"/>
+      <c r="OX25" s="21"/>
+      <c r="PB25" s="21"/>
+      <c r="PF25" s="21"/>
+      <c r="PJ25" s="21"/>
+      <c r="PN25" s="21"/>
+      <c r="PR25" s="21"/>
+      <c r="PV25" s="21"/>
+      <c r="PZ25" s="21"/>
+      <c r="QD25" s="21"/>
+      <c r="QH25" s="21"/>
+      <c r="QL25" s="21"/>
+      <c r="QP25" s="21"/>
+      <c r="QT25" s="21"/>
+      <c r="QX25" s="21"/>
+      <c r="RB25" s="21"/>
+      <c r="RF25" s="21"/>
+      <c r="RJ25" s="21"/>
+      <c r="RN25" s="21"/>
+      <c r="RR25" s="21"/>
+      <c r="RV25" s="21"/>
+      <c r="RZ25" s="21"/>
+      <c r="SD25" s="21"/>
+      <c r="SH25" s="21"/>
+      <c r="SL25" s="21"/>
+      <c r="SP25" s="21"/>
+      <c r="ST25" s="21"/>
+      <c r="SX25" s="21"/>
+      <c r="TB25" s="21"/>
+      <c r="TF25" s="21"/>
+      <c r="TJ25" s="21"/>
+      <c r="TN25" s="21"/>
+      <c r="TR25" s="21"/>
+      <c r="TV25" s="21"/>
+      <c r="TZ25" s="21"/>
+      <c r="UD25" s="21"/>
+      <c r="UH25" s="21"/>
+      <c r="UL25" s="21"/>
+      <c r="UP25" s="21"/>
+      <c r="UT25" s="21"/>
+      <c r="UX25" s="21"/>
+      <c r="VB25" s="21"/>
+      <c r="VF25" s="21"/>
+      <c r="VJ25" s="21"/>
+      <c r="VN25" s="21"/>
+      <c r="VR25" s="21"/>
+      <c r="VV25" s="21"/>
+      <c r="VZ25" s="21"/>
+      <c r="WD25" s="21"/>
+      <c r="WH25" s="21"/>
+      <c r="WL25" s="21"/>
+      <c r="WP25" s="21"/>
+      <c r="WT25" s="21"/>
+      <c r="WX25" s="21"/>
+      <c r="XB25" s="21"/>
+      <c r="XF25" s="21"/>
+      <c r="XJ25" s="21"/>
+      <c r="XN25" s="21"/>
+      <c r="XR25" s="21"/>
+      <c r="XV25" s="21"/>
+      <c r="XZ25" s="21"/>
+      <c r="YD25" s="21"/>
+      <c r="YH25" s="21"/>
+      <c r="YL25" s="21"/>
+      <c r="YP25" s="21"/>
+      <c r="YT25" s="21"/>
+      <c r="YX25" s="21"/>
+      <c r="ZB25" s="21"/>
+      <c r="ZF25" s="21"/>
+      <c r="ZJ25" s="21"/>
+      <c r="ZN25" s="21"/>
+      <c r="ZR25" s="21"/>
+      <c r="ZV25" s="21"/>
+      <c r="ZZ25" s="21"/>
+      <c r="AAD25" s="21"/>
+      <c r="AAH25" s="21"/>
+      <c r="AAL25" s="21"/>
+      <c r="AAP25" s="21"/>
+      <c r="AAT25" s="21"/>
+      <c r="AAX25" s="21"/>
+      <c r="ABB25" s="21"/>
+      <c r="ABF25" s="21"/>
+      <c r="ABJ25" s="21"/>
+      <c r="ABN25" s="21"/>
+      <c r="ABR25" s="21"/>
+      <c r="ABV25" s="21"/>
+      <c r="ABZ25" s="21"/>
+      <c r="ACD25" s="21"/>
+      <c r="ACH25" s="21"/>
+      <c r="ACL25" s="21"/>
+      <c r="ACP25" s="21"/>
+      <c r="ACT25" s="21"/>
+      <c r="ACX25" s="21"/>
+      <c r="ADB25" s="21"/>
+      <c r="ADF25" s="21"/>
+      <c r="ADJ25" s="21"/>
+      <c r="ADN25" s="21"/>
+      <c r="ADR25" s="21"/>
+      <c r="ADV25" s="21"/>
+      <c r="ADZ25" s="21"/>
+      <c r="AED25" s="21"/>
+      <c r="AEH25" s="21"/>
+      <c r="AEL25" s="21"/>
+      <c r="AEP25" s="21"/>
+      <c r="AET25" s="21"/>
+      <c r="AEX25" s="21"/>
+      <c r="AFB25" s="21"/>
+      <c r="AFF25" s="21"/>
+      <c r="AFJ25" s="21"/>
+      <c r="AFN25" s="21"/>
+      <c r="AFR25" s="21"/>
+      <c r="AFV25" s="21"/>
+      <c r="AFZ25" s="21"/>
+      <c r="AGD25" s="21"/>
+      <c r="AGH25" s="21"/>
+      <c r="AGL25" s="21"/>
+      <c r="AGP25" s="21"/>
+      <c r="AGT25" s="21"/>
+      <c r="AGX25" s="21"/>
+      <c r="AHB25" s="21"/>
+      <c r="AHF25" s="21"/>
+      <c r="AHJ25" s="21"/>
+      <c r="AHN25" s="21"/>
+      <c r="AHR25" s="21"/>
+      <c r="AHV25" s="21"/>
+      <c r="AHZ25" s="21"/>
+      <c r="AID25" s="21"/>
+      <c r="AIH25" s="21"/>
+      <c r="AIL25" s="21"/>
+      <c r="AIP25" s="21"/>
+      <c r="AIT25" s="21"/>
+      <c r="AIX25" s="21"/>
+      <c r="AJB25" s="21"/>
+      <c r="AJF25" s="21"/>
+      <c r="AJJ25" s="21"/>
+      <c r="AJN25" s="21"/>
+      <c r="AJR25" s="21"/>
+      <c r="AJV25" s="21"/>
+      <c r="AJZ25" s="21"/>
+      <c r="AKD25" s="21"/>
+      <c r="AKH25" s="21"/>
+      <c r="AKL25" s="21"/>
+      <c r="AKP25" s="21"/>
+      <c r="AKT25" s="21"/>
+      <c r="AKX25" s="21"/>
+      <c r="ALB25" s="21"/>
+      <c r="ALF25" s="21"/>
+      <c r="ALJ25" s="21"/>
+      <c r="ALN25" s="21"/>
+      <c r="ALR25" s="21"/>
+      <c r="ALV25" s="21"/>
+      <c r="ALZ25" s="21"/>
+      <c r="AMD25" s="21"/>
+      <c r="AMH25" s="21"/>
+      <c r="AML25" s="21"/>
+      <c r="AMP25" s="21"/>
+      <c r="AMT25" s="21"/>
+      <c r="AMX25" s="21"/>
+      <c r="ANB25" s="21"/>
+      <c r="ANF25" s="21"/>
+      <c r="ANJ25" s="21"/>
+      <c r="ANN25" s="21"/>
+      <c r="ANR25" s="21"/>
+      <c r="ANV25" s="21"/>
+      <c r="ANZ25" s="21"/>
+      <c r="AOD25" s="21"/>
+      <c r="AOH25" s="21"/>
+      <c r="AOL25" s="21"/>
+      <c r="AOP25" s="21"/>
+      <c r="AOT25" s="21"/>
+      <c r="AOX25" s="21"/>
+      <c r="APB25" s="21"/>
+      <c r="APF25" s="21"/>
+      <c r="APJ25" s="21"/>
+      <c r="APN25" s="21"/>
+      <c r="APR25" s="21"/>
+      <c r="APV25" s="21"/>
+      <c r="APZ25" s="21"/>
+      <c r="AQD25" s="21"/>
+      <c r="AQH25" s="21"/>
+      <c r="AQL25" s="21"/>
+      <c r="AQP25" s="21"/>
+      <c r="AQT25" s="21"/>
+      <c r="AQX25" s="21"/>
+      <c r="ARB25" s="21"/>
+      <c r="ARF25" s="21"/>
+      <c r="ARJ25" s="21"/>
+      <c r="ARN25" s="21"/>
+      <c r="ARR25" s="21"/>
+      <c r="ARV25" s="21"/>
+      <c r="ARZ25" s="21"/>
+      <c r="ASD25" s="21"/>
+      <c r="ASH25" s="21"/>
+      <c r="ASL25" s="21"/>
+      <c r="ASP25" s="21"/>
+      <c r="AST25" s="21"/>
+      <c r="ASX25" s="21"/>
+      <c r="ATB25" s="21"/>
+      <c r="ATF25" s="21"/>
+      <c r="ATJ25" s="21"/>
+      <c r="ATN25" s="21"/>
+      <c r="ATR25" s="21"/>
+      <c r="ATV25" s="21"/>
+      <c r="ATZ25" s="21"/>
+      <c r="AUD25" s="21"/>
+      <c r="AUH25" s="21"/>
+      <c r="AUL25" s="21"/>
+      <c r="AUP25" s="21"/>
+      <c r="AUT25" s="21"/>
+      <c r="AUX25" s="21"/>
+      <c r="AVB25" s="21"/>
+      <c r="AVF25" s="21"/>
+      <c r="AVJ25" s="21"/>
+      <c r="AVN25" s="21"/>
+      <c r="AVR25" s="21"/>
+      <c r="AVV25" s="21"/>
+      <c r="AVZ25" s="21"/>
+      <c r="AWD25" s="21"/>
+      <c r="AWH25" s="21"/>
+      <c r="AWL25" s="21"/>
+      <c r="AWP25" s="21"/>
+      <c r="AWT25" s="21"/>
+      <c r="AWX25" s="21"/>
+      <c r="AXB25" s="21"/>
+      <c r="AXF25" s="21"/>
+      <c r="AXJ25" s="21"/>
+      <c r="AXN25" s="21"/>
+      <c r="AXR25" s="21"/>
+      <c r="AXV25" s="21"/>
+      <c r="AXZ25" s="21"/>
+      <c r="AYD25" s="21"/>
+      <c r="AYH25" s="21"/>
+      <c r="AYL25" s="21"/>
+      <c r="AYP25" s="21"/>
+      <c r="AYT25" s="21"/>
+      <c r="AYX25" s="21"/>
+      <c r="AZB25" s="21"/>
+      <c r="AZF25" s="21"/>
+      <c r="AZJ25" s="21"/>
+      <c r="AZN25" s="21"/>
+      <c r="AZR25" s="21"/>
+      <c r="AZV25" s="21"/>
+      <c r="AZZ25" s="21"/>
+      <c r="BAD25" s="21"/>
+      <c r="BAH25" s="21"/>
+      <c r="BAL25" s="21"/>
+      <c r="BAP25" s="21"/>
+      <c r="BAT25" s="21"/>
+      <c r="BAX25" s="21"/>
+      <c r="BBB25" s="21"/>
+      <c r="BBF25" s="21"/>
+      <c r="BBJ25" s="21"/>
+      <c r="BBN25" s="21"/>
+      <c r="BBR25" s="21"/>
+      <c r="BBV25" s="21"/>
+      <c r="BBZ25" s="21"/>
+      <c r="BCD25" s="21"/>
+      <c r="BCH25" s="21"/>
+      <c r="BCL25" s="21"/>
+      <c r="BCP25" s="21"/>
+      <c r="BCT25" s="21"/>
+      <c r="BCX25" s="21"/>
+      <c r="BDB25" s="21"/>
+      <c r="BDF25" s="21"/>
+      <c r="BDJ25" s="21"/>
+      <c r="BDN25" s="21"/>
+      <c r="BDR25" s="21"/>
+      <c r="BDV25" s="21"/>
+      <c r="BDZ25" s="21"/>
+      <c r="BED25" s="21"/>
+      <c r="BEH25" s="21"/>
+      <c r="BEL25" s="21"/>
+      <c r="BEP25" s="21"/>
+      <c r="BET25" s="21"/>
+      <c r="BEX25" s="21"/>
+      <c r="BFB25" s="21"/>
+      <c r="BFF25" s="21"/>
+      <c r="BFJ25" s="21"/>
+      <c r="BFN25" s="21"/>
+      <c r="BFR25" s="21"/>
+      <c r="BFV25" s="21"/>
+      <c r="BFZ25" s="21"/>
+      <c r="BGD25" s="21"/>
+      <c r="BGH25" s="21"/>
+      <c r="BGL25" s="21"/>
+      <c r="BGP25" s="21"/>
+      <c r="BGT25" s="21"/>
+      <c r="BGX25" s="21"/>
+      <c r="BHB25" s="21"/>
+      <c r="BHF25" s="21"/>
+      <c r="BHJ25" s="21"/>
+      <c r="BHN25" s="21"/>
+      <c r="BHR25" s="21"/>
+      <c r="BHV25" s="21"/>
+      <c r="BHZ25" s="21"/>
+      <c r="BID25" s="21"/>
+      <c r="BIH25" s="21"/>
+      <c r="BIL25" s="21"/>
+      <c r="BIP25" s="21"/>
+      <c r="BIT25" s="21"/>
+      <c r="BIX25" s="21"/>
+      <c r="BJB25" s="21"/>
+      <c r="BJF25" s="21"/>
+      <c r="BJJ25" s="21"/>
+      <c r="BJN25" s="21"/>
+      <c r="BJR25" s="21"/>
+      <c r="BJV25" s="21"/>
+      <c r="BJZ25" s="21"/>
+      <c r="BKD25" s="21"/>
+      <c r="BKH25" s="21"/>
+      <c r="BKL25" s="21"/>
+      <c r="BKP25" s="21"/>
+      <c r="BKT25" s="21"/>
+      <c r="BKX25" s="21"/>
+      <c r="BLB25" s="21"/>
+      <c r="BLF25" s="21"/>
+      <c r="BLJ25" s="21"/>
+      <c r="BLN25" s="21"/>
+      <c r="BLR25" s="21"/>
+      <c r="BLV25" s="21"/>
+      <c r="BLZ25" s="21"/>
+      <c r="BMD25" s="21"/>
+      <c r="BMH25" s="21"/>
+      <c r="BML25" s="21"/>
+      <c r="BMP25" s="21"/>
+      <c r="BMT25" s="21"/>
+      <c r="BMX25" s="21"/>
+      <c r="BNB25" s="21"/>
+      <c r="BNF25" s="21"/>
+      <c r="BNJ25" s="21"/>
+      <c r="BNN25" s="21"/>
+      <c r="BNR25" s="21"/>
+      <c r="BNV25" s="21"/>
+      <c r="BNZ25" s="21"/>
+      <c r="BOD25" s="21"/>
+      <c r="BOH25" s="21"/>
+      <c r="BOL25" s="21"/>
+      <c r="BOP25" s="21"/>
+      <c r="BOT25" s="21"/>
+      <c r="BOX25" s="21"/>
+      <c r="BPB25" s="21"/>
+      <c r="BPF25" s="21"/>
+      <c r="BPJ25" s="21"/>
+      <c r="BPN25" s="21"/>
+      <c r="BPR25" s="21"/>
+      <c r="BPV25" s="21"/>
+      <c r="BPZ25" s="21"/>
+      <c r="BQD25" s="21"/>
+      <c r="BQH25" s="21"/>
+      <c r="BQL25" s="21"/>
+      <c r="BQP25" s="21"/>
+      <c r="BQT25" s="21"/>
+      <c r="BQX25" s="21"/>
+      <c r="BRB25" s="21"/>
+      <c r="BRF25" s="21"/>
+      <c r="BRJ25" s="21"/>
+      <c r="BRN25" s="21"/>
+      <c r="BRR25" s="21"/>
+      <c r="BRV25" s="21"/>
+      <c r="BRZ25" s="21"/>
+      <c r="BSD25" s="21"/>
+      <c r="BSH25" s="21"/>
+      <c r="BSL25" s="21"/>
+      <c r="BSP25" s="21"/>
+      <c r="BST25" s="21"/>
+      <c r="BSX25" s="21"/>
+      <c r="BTB25" s="21"/>
+      <c r="BTF25" s="21"/>
+      <c r="BTJ25" s="21"/>
+      <c r="BTN25" s="21"/>
+      <c r="BTR25" s="21"/>
+      <c r="BTV25" s="21"/>
+      <c r="BTZ25" s="21"/>
+      <c r="BUD25" s="21"/>
+      <c r="BUH25" s="21"/>
+      <c r="BUL25" s="21"/>
+      <c r="BUP25" s="21"/>
+      <c r="BUT25" s="21"/>
+      <c r="BUX25" s="21"/>
+      <c r="BVB25" s="21"/>
+      <c r="BVF25" s="21"/>
+      <c r="BVJ25" s="21"/>
+      <c r="BVN25" s="21"/>
+      <c r="BVR25" s="21"/>
+      <c r="BVV25" s="21"/>
+      <c r="BVZ25" s="21"/>
+      <c r="BWD25" s="21"/>
+      <c r="BWH25" s="21"/>
+      <c r="BWL25" s="21"/>
+      <c r="BWP25" s="21"/>
+      <c r="BWT25" s="21"/>
+      <c r="BWX25" s="21"/>
+      <c r="BXB25" s="21"/>
+      <c r="BXF25" s="21"/>
+      <c r="BXJ25" s="21"/>
+      <c r="BXN25" s="21"/>
+      <c r="BXR25" s="21"/>
+      <c r="BXV25" s="21"/>
+      <c r="BXZ25" s="21"/>
+      <c r="BYD25" s="21"/>
+      <c r="BYH25" s="21"/>
+      <c r="BYL25" s="21"/>
+      <c r="BYP25" s="21"/>
+      <c r="BYT25" s="21"/>
+      <c r="BYX25" s="21"/>
+      <c r="BZB25" s="21"/>
+      <c r="BZF25" s="21"/>
+      <c r="BZJ25" s="21"/>
+      <c r="BZN25" s="21"/>
+      <c r="BZR25" s="21"/>
+      <c r="BZV25" s="21"/>
+      <c r="BZZ25" s="21"/>
+      <c r="CAD25" s="21"/>
+      <c r="CAH25" s="21"/>
+      <c r="CAL25" s="21"/>
+      <c r="CAP25" s="21"/>
+      <c r="CAT25" s="21"/>
+      <c r="CAX25" s="21"/>
+      <c r="CBB25" s="21"/>
+      <c r="CBF25" s="21"/>
+      <c r="CBJ25" s="21"/>
+      <c r="CBN25" s="21"/>
+      <c r="CBR25" s="21"/>
+      <c r="CBV25" s="21"/>
+      <c r="CBZ25" s="21"/>
+      <c r="CCD25" s="21"/>
+      <c r="CCH25" s="21"/>
+      <c r="CCL25" s="21"/>
+      <c r="CCP25" s="21"/>
+      <c r="CCT25" s="21"/>
+      <c r="CCX25" s="21"/>
+      <c r="CDB25" s="21"/>
+      <c r="CDF25" s="21"/>
+      <c r="CDJ25" s="21"/>
+      <c r="CDN25" s="21"/>
+      <c r="CDR25" s="21"/>
+      <c r="CDV25" s="21"/>
+      <c r="CDZ25" s="21"/>
+      <c r="CED25" s="21"/>
+      <c r="CEH25" s="21"/>
+      <c r="CEL25" s="21"/>
+      <c r="CEP25" s="21"/>
+      <c r="CET25" s="21"/>
+      <c r="CEX25" s="21"/>
+      <c r="CFB25" s="21"/>
+      <c r="CFF25" s="21"/>
+      <c r="CFJ25" s="21"/>
+      <c r="CFN25" s="21"/>
+      <c r="CFR25" s="21"/>
+      <c r="CFV25" s="21"/>
+      <c r="CFZ25" s="21"/>
+      <c r="CGD25" s="21"/>
+      <c r="CGH25" s="21"/>
+      <c r="CGL25" s="21"/>
+      <c r="CGP25" s="21"/>
+      <c r="CGT25" s="21"/>
+      <c r="CGX25" s="21"/>
+      <c r="CHB25" s="21"/>
+      <c r="CHF25" s="21"/>
+      <c r="CHJ25" s="21"/>
+      <c r="CHN25" s="21"/>
+      <c r="CHR25" s="21"/>
+      <c r="CHV25" s="21"/>
+      <c r="CHZ25" s="21"/>
+      <c r="CID25" s="21"/>
+      <c r="CIH25" s="21"/>
+      <c r="CIL25" s="21"/>
+      <c r="CIP25" s="21"/>
+      <c r="CIT25" s="21"/>
+      <c r="CIX25" s="21"/>
+      <c r="CJB25" s="21"/>
+      <c r="CJF25" s="21"/>
+      <c r="CJJ25" s="21"/>
+      <c r="CJN25" s="21"/>
+      <c r="CJR25" s="21"/>
+      <c r="CJV25" s="21"/>
+      <c r="CJZ25" s="21"/>
+      <c r="CKD25" s="21"/>
+      <c r="CKH25" s="21"/>
+      <c r="CKL25" s="21"/>
+      <c r="CKP25" s="21"/>
+      <c r="CKT25" s="21"/>
+      <c r="CKX25" s="21"/>
+      <c r="CLB25" s="21"/>
+      <c r="CLF25" s="21"/>
+      <c r="CLJ25" s="21"/>
+      <c r="CLN25" s="21"/>
+      <c r="CLR25" s="21"/>
+      <c r="CLV25" s="21"/>
+      <c r="CLZ25" s="21"/>
+      <c r="CMD25" s="21"/>
+      <c r="CMH25" s="21"/>
+      <c r="CML25" s="21"/>
+      <c r="CMP25" s="21"/>
+      <c r="CMT25" s="21"/>
+      <c r="CMX25" s="21"/>
+      <c r="CNB25" s="21"/>
+      <c r="CNF25" s="21"/>
+      <c r="CNJ25" s="21"/>
+      <c r="CNN25" s="21"/>
+      <c r="CNR25" s="21"/>
+      <c r="CNV25" s="21"/>
+      <c r="CNZ25" s="21"/>
+      <c r="COD25" s="21"/>
+      <c r="COH25" s="21"/>
+      <c r="COL25" s="21"/>
+      <c r="COP25" s="21"/>
+      <c r="COT25" s="21"/>
+      <c r="COX25" s="21"/>
+      <c r="CPB25" s="21"/>
+      <c r="CPF25" s="21"/>
+      <c r="CPJ25" s="21"/>
+      <c r="CPN25" s="21"/>
+      <c r="CPR25" s="21"/>
+      <c r="CPV25" s="21"/>
+      <c r="CPZ25" s="21"/>
+      <c r="CQD25" s="21"/>
+      <c r="CQH25" s="21"/>
+      <c r="CQL25" s="21"/>
+      <c r="CQP25" s="21"/>
+      <c r="CQT25" s="21"/>
+      <c r="CQX25" s="21"/>
+      <c r="CRB25" s="21"/>
+      <c r="CRF25" s="21"/>
+      <c r="CRJ25" s="21"/>
+      <c r="CRN25" s="21"/>
+      <c r="CRR25" s="21"/>
+      <c r="CRV25" s="21"/>
+      <c r="CRZ25" s="21"/>
+      <c r="CSD25" s="21"/>
+      <c r="CSH25" s="21"/>
+      <c r="CSL25" s="21"/>
+      <c r="CSP25" s="21"/>
+      <c r="CST25" s="21"/>
+      <c r="CSX25" s="21"/>
+      <c r="CTB25" s="21"/>
+      <c r="CTF25" s="21"/>
+      <c r="CTJ25" s="21"/>
+      <c r="CTN25" s="21"/>
+      <c r="CTR25" s="21"/>
+      <c r="CTV25" s="21"/>
+      <c r="CTZ25" s="21"/>
+      <c r="CUD25" s="21"/>
+      <c r="CUH25" s="21"/>
+      <c r="CUL25" s="21"/>
+      <c r="CUP25" s="21"/>
+      <c r="CUT25" s="21"/>
+      <c r="CUX25" s="21"/>
+      <c r="CVB25" s="21"/>
+      <c r="CVF25" s="21"/>
+      <c r="CVJ25" s="21"/>
+      <c r="CVN25" s="21"/>
+      <c r="CVR25" s="21"/>
+      <c r="CVV25" s="21"/>
+      <c r="CVZ25" s="21"/>
+      <c r="CWD25" s="21"/>
+      <c r="CWH25" s="21"/>
+      <c r="CWL25" s="21"/>
+      <c r="CWP25" s="21"/>
+      <c r="CWT25" s="21"/>
+      <c r="CWX25" s="21"/>
+      <c r="CXB25" s="21"/>
+      <c r="CXF25" s="21"/>
+      <c r="CXJ25" s="21"/>
+      <c r="CXN25" s="21"/>
+      <c r="CXR25" s="21"/>
+      <c r="CXV25" s="21"/>
+      <c r="CXZ25" s="21"/>
+      <c r="CYD25" s="21"/>
+      <c r="CYH25" s="21"/>
+      <c r="CYL25" s="21"/>
+      <c r="CYP25" s="21"/>
+      <c r="CYT25" s="21"/>
+      <c r="CYX25" s="21"/>
+      <c r="CZB25" s="21"/>
+      <c r="CZF25" s="21"/>
+      <c r="CZJ25" s="21"/>
+      <c r="CZN25" s="21"/>
+      <c r="CZR25" s="21"/>
+      <c r="CZV25" s="21"/>
+      <c r="CZZ25" s="21"/>
+      <c r="DAD25" s="21"/>
+      <c r="DAH25" s="21"/>
+      <c r="DAL25" s="21"/>
+      <c r="DAP25" s="21"/>
+      <c r="DAT25" s="21"/>
+      <c r="DAX25" s="21"/>
+      <c r="DBB25" s="21"/>
+      <c r="DBF25" s="21"/>
+      <c r="DBJ25" s="21"/>
+      <c r="DBN25" s="21"/>
+      <c r="DBR25" s="21"/>
+      <c r="DBV25" s="21"/>
+      <c r="DBZ25" s="21"/>
+      <c r="DCD25" s="21"/>
+      <c r="DCH25" s="21"/>
+      <c r="DCL25" s="21"/>
+      <c r="DCP25" s="21"/>
+      <c r="DCT25" s="21"/>
+      <c r="DCX25" s="21"/>
+      <c r="DDB25" s="21"/>
+      <c r="DDF25" s="21"/>
+      <c r="DDJ25" s="21"/>
+      <c r="DDN25" s="21"/>
+      <c r="DDR25" s="21"/>
+      <c r="DDV25" s="21"/>
+      <c r="DDZ25" s="21"/>
+      <c r="DED25" s="21"/>
+      <c r="DEH25" s="21"/>
+      <c r="DEL25" s="21"/>
+      <c r="DEP25" s="21"/>
+      <c r="DET25" s="21"/>
+      <c r="DEX25" s="21"/>
+      <c r="DFB25" s="21"/>
+      <c r="DFF25" s="21"/>
+      <c r="DFJ25" s="21"/>
+      <c r="DFN25" s="21"/>
+      <c r="DFR25" s="21"/>
+      <c r="DFV25" s="21"/>
+      <c r="DFZ25" s="21"/>
+      <c r="DGD25" s="21"/>
+      <c r="DGH25" s="21"/>
+      <c r="DGL25" s="21"/>
+      <c r="DGP25" s="21"/>
+      <c r="DGT25" s="21"/>
+      <c r="DGX25" s="21"/>
+      <c r="DHB25" s="21"/>
+      <c r="DHF25" s="21"/>
+      <c r="DHJ25" s="21"/>
+      <c r="DHN25" s="21"/>
+      <c r="DHR25" s="21"/>
+      <c r="DHV25" s="21"/>
+      <c r="DHZ25" s="21"/>
+      <c r="DID25" s="21"/>
+      <c r="DIH25" s="21"/>
+      <c r="DIL25" s="21"/>
+      <c r="DIP25" s="21"/>
+      <c r="DIT25" s="21"/>
+      <c r="DIX25" s="21"/>
+      <c r="DJB25" s="21"/>
+      <c r="DJF25" s="21"/>
+      <c r="DJJ25" s="21"/>
+      <c r="DJN25" s="21"/>
+      <c r="DJR25" s="21"/>
+      <c r="DJV25" s="21"/>
+      <c r="DJZ25" s="21"/>
+      <c r="DKD25" s="21"/>
+      <c r="DKH25" s="21"/>
+      <c r="DKL25" s="21"/>
+      <c r="DKP25" s="21"/>
+      <c r="DKT25" s="21"/>
+      <c r="DKX25" s="21"/>
+      <c r="DLB25" s="21"/>
+      <c r="DLF25" s="21"/>
+      <c r="DLJ25" s="21"/>
+      <c r="DLN25" s="21"/>
+      <c r="DLR25" s="21"/>
+      <c r="DLV25" s="21"/>
+      <c r="DLZ25" s="21"/>
+      <c r="DMD25" s="21"/>
+      <c r="DMH25" s="21"/>
+      <c r="DML25" s="21"/>
+      <c r="DMP25" s="21"/>
+      <c r="DMT25" s="21"/>
+      <c r="DMX25" s="21"/>
+      <c r="DNB25" s="21"/>
+      <c r="DNF25" s="21"/>
+      <c r="DNJ25" s="21"/>
+      <c r="DNN25" s="21"/>
+      <c r="DNR25" s="21"/>
+      <c r="DNV25" s="21"/>
+      <c r="DNZ25" s="21"/>
+      <c r="DOD25" s="21"/>
+      <c r="DOH25" s="21"/>
+      <c r="DOL25" s="21"/>
+      <c r="DOP25" s="21"/>
+      <c r="DOT25" s="21"/>
+      <c r="DOX25" s="21"/>
+      <c r="DPB25" s="21"/>
+      <c r="DPF25" s="21"/>
+      <c r="DPJ25" s="21"/>
+      <c r="DPN25" s="21"/>
+      <c r="DPR25" s="21"/>
+      <c r="DPV25" s="21"/>
+      <c r="DPZ25" s="21"/>
+      <c r="DQD25" s="21"/>
+      <c r="DQH25" s="21"/>
+      <c r="DQL25" s="21"/>
+      <c r="DQP25" s="21"/>
+      <c r="DQT25" s="21"/>
+      <c r="DQX25" s="21"/>
+      <c r="DRB25" s="21"/>
+      <c r="DRF25" s="21"/>
+      <c r="DRJ25" s="21"/>
+      <c r="DRN25" s="21"/>
+      <c r="DRR25" s="21"/>
+      <c r="DRV25" s="21"/>
+      <c r="DRZ25" s="21"/>
+      <c r="DSD25" s="21"/>
+      <c r="DSH25" s="21"/>
+      <c r="DSL25" s="21"/>
+      <c r="DSP25" s="21"/>
+      <c r="DST25" s="21"/>
+      <c r="DSX25" s="21"/>
+      <c r="DTB25" s="21"/>
+      <c r="DTF25" s="21"/>
+      <c r="DTJ25" s="21"/>
+      <c r="DTN25" s="21"/>
+      <c r="DTR25" s="21"/>
+      <c r="DTV25" s="21"/>
+      <c r="DTZ25" s="21"/>
+      <c r="DUD25" s="21"/>
+      <c r="DUH25" s="21"/>
+      <c r="DUL25" s="21"/>
+      <c r="DUP25" s="21"/>
+      <c r="DUT25" s="21"/>
+      <c r="DUX25" s="21"/>
+      <c r="DVB25" s="21"/>
+      <c r="DVF25" s="21"/>
+      <c r="DVJ25" s="21"/>
+      <c r="DVN25" s="21"/>
+      <c r="DVR25" s="21"/>
+      <c r="DVV25" s="21"/>
+      <c r="DVZ25" s="21"/>
+      <c r="DWD25" s="21"/>
+      <c r="DWH25" s="21"/>
+      <c r="DWL25" s="21"/>
+      <c r="DWP25" s="21"/>
+      <c r="DWT25" s="21"/>
+      <c r="DWX25" s="21"/>
+      <c r="DXB25" s="21"/>
+      <c r="DXF25" s="21"/>
+      <c r="DXJ25" s="21"/>
+      <c r="DXN25" s="21"/>
+      <c r="DXR25" s="21"/>
+      <c r="DXV25" s="21"/>
+      <c r="DXZ25" s="21"/>
+      <c r="DYD25" s="21"/>
+      <c r="DYH25" s="21"/>
+      <c r="DYL25" s="21"/>
+      <c r="DYP25" s="21"/>
+      <c r="DYT25" s="21"/>
+      <c r="DYX25" s="21"/>
+      <c r="DZB25" s="21"/>
+      <c r="DZF25" s="21"/>
+      <c r="DZJ25" s="21"/>
+      <c r="DZN25" s="21"/>
+      <c r="DZR25" s="21"/>
+      <c r="DZV25" s="21"/>
+      <c r="DZZ25" s="21"/>
+      <c r="EAD25" s="21"/>
+      <c r="EAH25" s="21"/>
+      <c r="EAL25" s="21"/>
+      <c r="EAP25" s="21"/>
+      <c r="EAT25" s="21"/>
+      <c r="EAX25" s="21"/>
+      <c r="EBB25" s="21"/>
+      <c r="EBF25" s="21"/>
+      <c r="EBJ25" s="21"/>
+      <c r="EBN25" s="21"/>
+      <c r="EBR25" s="21"/>
+      <c r="EBV25" s="21"/>
+      <c r="EBZ25" s="21"/>
+      <c r="ECD25" s="21"/>
+      <c r="ECH25" s="21"/>
+      <c r="ECL25" s="21"/>
+      <c r="ECP25" s="21"/>
+      <c r="ECT25" s="21"/>
+      <c r="ECX25" s="21"/>
+      <c r="EDB25" s="21"/>
+      <c r="EDF25" s="21"/>
+      <c r="EDJ25" s="21"/>
+      <c r="EDN25" s="21"/>
+      <c r="EDR25" s="21"/>
+      <c r="EDV25" s="21"/>
+      <c r="EDZ25" s="21"/>
+      <c r="EED25" s="21"/>
+      <c r="EEH25" s="21"/>
+      <c r="EEL25" s="21"/>
+      <c r="EEP25" s="21"/>
+      <c r="EET25" s="21"/>
+      <c r="EEX25" s="21"/>
+      <c r="EFB25" s="21"/>
+      <c r="EFF25" s="21"/>
+      <c r="EFJ25" s="21"/>
+      <c r="EFN25" s="21"/>
+      <c r="EFR25" s="21"/>
+      <c r="EFV25" s="21"/>
+      <c r="EFZ25" s="21"/>
+      <c r="EGD25" s="21"/>
+      <c r="EGH25" s="21"/>
+      <c r="EGL25" s="21"/>
+      <c r="EGP25" s="21"/>
+      <c r="EGT25" s="21"/>
+      <c r="EGX25" s="21"/>
+      <c r="EHB25" s="21"/>
+      <c r="EHF25" s="21"/>
+      <c r="EHJ25" s="21"/>
+      <c r="EHN25" s="21"/>
+      <c r="EHR25" s="21"/>
+      <c r="EHV25" s="21"/>
+      <c r="EHZ25" s="21"/>
+      <c r="EID25" s="21"/>
+      <c r="EIH25" s="21"/>
+      <c r="EIL25" s="21"/>
+      <c r="EIP25" s="21"/>
+      <c r="EIT25" s="21"/>
+      <c r="EIX25" s="21"/>
+      <c r="EJB25" s="21"/>
+      <c r="EJF25" s="21"/>
+      <c r="EJJ25" s="21"/>
+      <c r="EJN25" s="21"/>
+      <c r="EJR25" s="21"/>
+      <c r="EJV25" s="21"/>
+      <c r="EJZ25" s="21"/>
+      <c r="EKD25" s="21"/>
+      <c r="EKH25" s="21"/>
+      <c r="EKL25" s="21"/>
+      <c r="EKP25" s="21"/>
+      <c r="EKT25" s="21"/>
+      <c r="EKX25" s="21"/>
+      <c r="ELB25" s="21"/>
+      <c r="ELF25" s="21"/>
+      <c r="ELJ25" s="21"/>
+      <c r="ELN25" s="21"/>
+      <c r="ELR25" s="21"/>
+      <c r="ELV25" s="21"/>
+      <c r="ELZ25" s="21"/>
+      <c r="EMD25" s="21"/>
+      <c r="EMH25" s="21"/>
+      <c r="EML25" s="21"/>
+      <c r="EMP25" s="21"/>
+      <c r="EMT25" s="21"/>
+      <c r="EMX25" s="21"/>
+      <c r="ENB25" s="21"/>
+      <c r="ENF25" s="21"/>
+      <c r="ENJ25" s="21"/>
+      <c r="ENN25" s="21"/>
+      <c r="ENR25" s="21"/>
+      <c r="ENV25" s="21"/>
+      <c r="ENZ25" s="21"/>
+      <c r="EOD25" s="21"/>
+      <c r="EOH25" s="21"/>
+      <c r="EOL25" s="21"/>
+      <c r="EOP25" s="21"/>
+      <c r="EOT25" s="21"/>
+      <c r="EOX25" s="21"/>
+      <c r="EPB25" s="21"/>
+      <c r="EPF25" s="21"/>
+      <c r="EPJ25" s="21"/>
+      <c r="EPN25" s="21"/>
+      <c r="EPR25" s="21"/>
+      <c r="EPV25" s="21"/>
+      <c r="EPZ25" s="21"/>
+      <c r="EQD25" s="21"/>
+      <c r="EQH25" s="21"/>
+      <c r="EQL25" s="21"/>
+      <c r="EQP25" s="21"/>
+      <c r="EQT25" s="21"/>
+      <c r="EQX25" s="21"/>
+      <c r="ERB25" s="21"/>
+      <c r="ERF25" s="21"/>
+      <c r="ERJ25" s="21"/>
+      <c r="ERN25" s="21"/>
+      <c r="ERR25" s="21"/>
+      <c r="ERV25" s="21"/>
+      <c r="ERZ25" s="21"/>
+      <c r="ESD25" s="21"/>
+      <c r="ESH25" s="21"/>
+      <c r="ESL25" s="21"/>
+      <c r="ESP25" s="21"/>
+      <c r="EST25" s="21"/>
+      <c r="ESX25" s="21"/>
+      <c r="ETB25" s="21"/>
+      <c r="ETF25" s="21"/>
+      <c r="ETJ25" s="21"/>
+      <c r="ETN25" s="21"/>
+      <c r="ETR25" s="21"/>
+      <c r="ETV25" s="21"/>
+      <c r="ETZ25" s="21"/>
+      <c r="EUD25" s="21"/>
+      <c r="EUH25" s="21"/>
+      <c r="EUL25" s="21"/>
+      <c r="EUP25" s="21"/>
+      <c r="EUT25" s="21"/>
+      <c r="EUX25" s="21"/>
+      <c r="EVB25" s="21"/>
+      <c r="EVF25" s="21"/>
+      <c r="EVJ25" s="21"/>
+      <c r="EVN25" s="21"/>
+      <c r="EVR25" s="21"/>
+      <c r="EVV25" s="21"/>
+      <c r="EVZ25" s="21"/>
+      <c r="EWD25" s="21"/>
+      <c r="EWH25" s="21"/>
+      <c r="EWL25" s="21"/>
+      <c r="EWP25" s="21"/>
+      <c r="EWT25" s="21"/>
+      <c r="EWX25" s="21"/>
+      <c r="EXB25" s="21"/>
+      <c r="EXF25" s="21"/>
+      <c r="EXJ25" s="21"/>
+      <c r="EXN25" s="21"/>
+      <c r="EXR25" s="21"/>
+      <c r="EXV25" s="21"/>
+      <c r="EXZ25" s="21"/>
+      <c r="EYD25" s="21"/>
+      <c r="EYH25" s="21"/>
+      <c r="EYL25" s="21"/>
+      <c r="EYP25" s="21"/>
+      <c r="EYT25" s="21"/>
+      <c r="EYX25" s="21"/>
+      <c r="EZB25" s="21"/>
+      <c r="EZF25" s="21"/>
+      <c r="EZJ25" s="21"/>
+      <c r="EZN25" s="21"/>
+      <c r="EZR25" s="21"/>
+      <c r="EZV25" s="21"/>
+      <c r="EZZ25" s="21"/>
+      <c r="FAD25" s="21"/>
+      <c r="FAH25" s="21"/>
+      <c r="FAL25" s="21"/>
+      <c r="FAP25" s="21"/>
+      <c r="FAT25" s="21"/>
+      <c r="FAX25" s="21"/>
+      <c r="FBB25" s="21"/>
+      <c r="FBF25" s="21"/>
+      <c r="FBJ25" s="21"/>
+      <c r="FBN25" s="21"/>
+      <c r="FBR25" s="21"/>
+      <c r="FBV25" s="21"/>
+      <c r="FBZ25" s="21"/>
+      <c r="FCD25" s="21"/>
+      <c r="FCH25" s="21"/>
+      <c r="FCL25" s="21"/>
+      <c r="FCP25" s="21"/>
+      <c r="FCT25" s="21"/>
+      <c r="FCX25" s="21"/>
+      <c r="FDB25" s="21"/>
+      <c r="FDF25" s="21"/>
+      <c r="FDJ25" s="21"/>
+      <c r="FDN25" s="21"/>
+      <c r="FDR25" s="21"/>
+      <c r="FDV25" s="21"/>
+      <c r="FDZ25" s="21"/>
+      <c r="FED25" s="21"/>
+      <c r="FEH25" s="21"/>
+      <c r="FEL25" s="21"/>
+      <c r="FEP25" s="21"/>
+      <c r="FET25" s="21"/>
+      <c r="FEX25" s="21"/>
+      <c r="FFB25" s="21"/>
+      <c r="FFF25" s="21"/>
+      <c r="FFJ25" s="21"/>
+      <c r="FFN25" s="21"/>
+      <c r="FFR25" s="21"/>
+      <c r="FFV25" s="21"/>
+      <c r="FFZ25" s="21"/>
+      <c r="FGD25" s="21"/>
+      <c r="FGH25" s="21"/>
+      <c r="FGL25" s="21"/>
+      <c r="FGP25" s="21"/>
+      <c r="FGT25" s="21"/>
+      <c r="FGX25" s="21"/>
+      <c r="FHB25" s="21"/>
+      <c r="FHF25" s="21"/>
+      <c r="FHJ25" s="21"/>
+      <c r="FHN25" s="21"/>
+      <c r="FHR25" s="21"/>
+      <c r="FHV25" s="21"/>
+      <c r="FHZ25" s="21"/>
+      <c r="FID25" s="21"/>
+      <c r="FIH25" s="21"/>
+      <c r="FIL25" s="21"/>
+      <c r="FIP25" s="21"/>
+      <c r="FIT25" s="21"/>
+      <c r="FIX25" s="21"/>
+      <c r="FJB25" s="21"/>
+      <c r="FJF25" s="21"/>
+      <c r="FJJ25" s="21"/>
+      <c r="FJN25" s="21"/>
+      <c r="FJR25" s="21"/>
+      <c r="FJV25" s="21"/>
+      <c r="FJZ25" s="21"/>
+      <c r="FKD25" s="21"/>
+      <c r="FKH25" s="21"/>
+      <c r="FKL25" s="21"/>
+      <c r="FKP25" s="21"/>
+      <c r="FKT25" s="21"/>
+      <c r="FKX25" s="21"/>
+      <c r="FLB25" s="21"/>
+      <c r="FLF25" s="21"/>
+      <c r="FLJ25" s="21"/>
+      <c r="FLN25" s="21"/>
+      <c r="FLR25" s="21"/>
+      <c r="FLV25" s="21"/>
+      <c r="FLZ25" s="21"/>
+      <c r="FMD25" s="21"/>
+      <c r="FMH25" s="21"/>
+      <c r="FML25" s="21"/>
+      <c r="FMP25" s="21"/>
+      <c r="FMT25" s="21"/>
+      <c r="FMX25" s="21"/>
+      <c r="FNB25" s="21"/>
+      <c r="FNF25" s="21"/>
+      <c r="FNJ25" s="21"/>
+      <c r="FNN25" s="21"/>
+      <c r="FNR25" s="21"/>
+      <c r="FNV25" s="21"/>
+      <c r="FNZ25" s="21"/>
+      <c r="FOD25" s="21"/>
+      <c r="FOH25" s="21"/>
+      <c r="FOL25" s="21"/>
+      <c r="FOP25" s="21"/>
+      <c r="FOT25" s="21"/>
+      <c r="FOX25" s="21"/>
+      <c r="FPB25" s="21"/>
+      <c r="FPF25" s="21"/>
+      <c r="FPJ25" s="21"/>
+      <c r="FPN25" s="21"/>
+      <c r="FPR25" s="21"/>
+      <c r="FPV25" s="21"/>
+      <c r="FPZ25" s="21"/>
+      <c r="FQD25" s="21"/>
+      <c r="FQH25" s="21"/>
+      <c r="FQL25" s="21"/>
+      <c r="FQP25" s="21"/>
+      <c r="FQT25" s="21"/>
+      <c r="FQX25" s="21"/>
+      <c r="FRB25" s="21"/>
+      <c r="FRF25" s="21"/>
+      <c r="FRJ25" s="21"/>
+      <c r="FRN25" s="21"/>
+      <c r="FRR25" s="21"/>
+      <c r="FRV25" s="21"/>
+      <c r="FRZ25" s="21"/>
+      <c r="FSD25" s="21"/>
+      <c r="FSH25" s="21"/>
+      <c r="FSL25" s="21"/>
+      <c r="FSP25" s="21"/>
+      <c r="FST25" s="21"/>
+      <c r="FSX25" s="21"/>
+      <c r="FTB25" s="21"/>
+      <c r="FTF25" s="21"/>
+      <c r="FTJ25" s="21"/>
+      <c r="FTN25" s="21"/>
+      <c r="FTR25" s="21"/>
+      <c r="FTV25" s="21"/>
+      <c r="FTZ25" s="21"/>
+      <c r="FUD25" s="21"/>
+      <c r="FUH25" s="21"/>
+      <c r="FUL25" s="21"/>
+      <c r="FUP25" s="21"/>
+      <c r="FUT25" s="21"/>
+      <c r="FUX25" s="21"/>
+      <c r="FVB25" s="21"/>
+      <c r="FVF25" s="21"/>
+      <c r="FVJ25" s="21"/>
+      <c r="FVN25" s="21"/>
+      <c r="FVR25" s="21"/>
+      <c r="FVV25" s="21"/>
+      <c r="FVZ25" s="21"/>
+      <c r="FWD25" s="21"/>
+      <c r="FWH25" s="21"/>
+      <c r="FWL25" s="21"/>
+      <c r="FWP25" s="21"/>
+      <c r="FWT25" s="21"/>
+      <c r="FWX25" s="21"/>
+      <c r="FXB25" s="21"/>
+      <c r="FXF25" s="21"/>
+      <c r="FXJ25" s="21"/>
+      <c r="FXN25" s="21"/>
+      <c r="FXR25" s="21"/>
+      <c r="FXV25" s="21"/>
+      <c r="FXZ25" s="21"/>
+      <c r="FYD25" s="21"/>
+      <c r="FYH25" s="21"/>
+      <c r="FYL25" s="21"/>
+      <c r="FYP25" s="21"/>
+      <c r="FYT25" s="21"/>
+      <c r="FYX25" s="21"/>
+      <c r="FZB25" s="21"/>
+      <c r="FZF25" s="21"/>
+      <c r="FZJ25" s="21"/>
+      <c r="FZN25" s="21"/>
+      <c r="FZR25" s="21"/>
+      <c r="FZV25" s="21"/>
+      <c r="FZZ25" s="21"/>
+      <c r="GAD25" s="21"/>
+      <c r="GAH25" s="21"/>
+      <c r="GAL25" s="21"/>
+      <c r="GAP25" s="21"/>
+      <c r="GAT25" s="21"/>
+      <c r="GAX25" s="21"/>
+      <c r="GBB25" s="21"/>
+      <c r="GBF25" s="21"/>
+      <c r="GBJ25" s="21"/>
+      <c r="GBN25" s="21"/>
+      <c r="GBR25" s="21"/>
+      <c r="GBV25" s="21"/>
+      <c r="GBZ25" s="21"/>
+      <c r="GCD25" s="21"/>
+      <c r="GCH25" s="21"/>
+      <c r="GCL25" s="21"/>
+      <c r="GCP25" s="21"/>
+      <c r="GCT25" s="21"/>
+      <c r="GCX25" s="21"/>
+      <c r="GDB25" s="21"/>
+      <c r="GDF25" s="21"/>
+      <c r="GDJ25" s="21"/>
+      <c r="GDN25" s="21"/>
+      <c r="GDR25" s="21"/>
+      <c r="GDV25" s="21"/>
+      <c r="GDZ25" s="21"/>
+      <c r="GED25" s="21"/>
+      <c r="GEH25" s="21"/>
+      <c r="GEL25" s="21"/>
+      <c r="GEP25" s="21"/>
+      <c r="GET25" s="21"/>
+      <c r="GEX25" s="21"/>
+      <c r="GFB25" s="21"/>
+      <c r="GFF25" s="21"/>
+      <c r="GFJ25" s="21"/>
+      <c r="GFN25" s="21"/>
+      <c r="GFR25" s="21"/>
+      <c r="GFV25" s="21"/>
+      <c r="GFZ25" s="21"/>
+      <c r="GGD25" s="21"/>
+      <c r="GGH25" s="21"/>
+      <c r="GGL25" s="21"/>
+      <c r="GGP25" s="21"/>
+      <c r="GGT25" s="21"/>
+      <c r="GGX25" s="21"/>
+      <c r="GHB25" s="21"/>
+      <c r="GHF25" s="21"/>
+      <c r="GHJ25" s="21"/>
+      <c r="GHN25" s="21"/>
+      <c r="GHR25" s="21"/>
+      <c r="GHV25" s="21"/>
+      <c r="GHZ25" s="21"/>
+      <c r="GID25" s="21"/>
+      <c r="GIH25" s="21"/>
+      <c r="GIL25" s="21"/>
+      <c r="GIP25" s="21"/>
+      <c r="GIT25" s="21"/>
+      <c r="GIX25" s="21"/>
+      <c r="GJB25" s="21"/>
+      <c r="GJF25" s="21"/>
+      <c r="GJJ25" s="21"/>
+      <c r="GJN25" s="21"/>
+      <c r="GJR25" s="21"/>
+      <c r="GJV25" s="21"/>
+      <c r="GJZ25" s="21"/>
+      <c r="GKD25" s="21"/>
+      <c r="GKH25" s="21"/>
+      <c r="GKL25" s="21"/>
+      <c r="GKP25" s="21"/>
+      <c r="GKT25" s="21"/>
+      <c r="GKX25" s="21"/>
+      <c r="GLB25" s="21"/>
+      <c r="GLF25" s="21"/>
+      <c r="GLJ25" s="21"/>
+      <c r="GLN25" s="21"/>
+      <c r="GLR25" s="21"/>
+      <c r="GLV25" s="21"/>
+      <c r="GLZ25" s="21"/>
+      <c r="GMD25" s="21"/>
+      <c r="GMH25" s="21"/>
+      <c r="GML25" s="21"/>
+      <c r="GMP25" s="21"/>
+      <c r="GMT25" s="21"/>
+      <c r="GMX25" s="21"/>
+      <c r="GNB25" s="21"/>
+      <c r="GNF25" s="21"/>
+      <c r="GNJ25" s="21"/>
+      <c r="GNN25" s="21"/>
+      <c r="GNR25" s="21"/>
+      <c r="GNV25" s="21"/>
+      <c r="GNZ25" s="21"/>
+      <c r="GOD25" s="21"/>
+      <c r="GOH25" s="21"/>
+      <c r="GOL25" s="21"/>
+      <c r="GOP25" s="21"/>
+      <c r="GOT25" s="21"/>
+      <c r="GOX25" s="21"/>
+      <c r="GPB25" s="21"/>
+      <c r="GPF25" s="21"/>
+      <c r="GPJ25" s="21"/>
+      <c r="GPN25" s="21"/>
+      <c r="GPR25" s="21"/>
+      <c r="GPV25" s="21"/>
+      <c r="GPZ25" s="21"/>
+      <c r="GQD25" s="21"/>
+      <c r="GQH25" s="21"/>
+      <c r="GQL25" s="21"/>
+      <c r="GQP25" s="21"/>
+      <c r="GQT25" s="21"/>
+      <c r="GQX25" s="21"/>
+      <c r="GRB25" s="21"/>
+      <c r="GRF25" s="21"/>
+      <c r="GRJ25" s="21"/>
+      <c r="GRN25" s="21"/>
+      <c r="GRR25" s="21"/>
+      <c r="GRV25" s="21"/>
+      <c r="GRZ25" s="21"/>
+      <c r="GSD25" s="21"/>
+      <c r="GSH25" s="21"/>
+      <c r="GSL25" s="21"/>
+      <c r="GSP25" s="21"/>
+      <c r="GST25" s="21"/>
+      <c r="GSX25" s="21"/>
+      <c r="GTB25" s="21"/>
+      <c r="GTF25" s="21"/>
+      <c r="GTJ25" s="21"/>
+      <c r="GTN25" s="21"/>
+      <c r="GTR25" s="21"/>
+      <c r="GTV25" s="21"/>
+      <c r="GTZ25" s="21"/>
+      <c r="GUD25" s="21"/>
+      <c r="GUH25" s="21"/>
+      <c r="GUL25" s="21"/>
+      <c r="GUP25" s="21"/>
+      <c r="GUT25" s="21"/>
+      <c r="GUX25" s="21"/>
+      <c r="GVB25" s="21"/>
+      <c r="GVF25" s="21"/>
+      <c r="GVJ25" s="21"/>
+      <c r="GVN25" s="21"/>
+      <c r="GVR25" s="21"/>
+      <c r="GVV25" s="21"/>
+      <c r="GVZ25" s="21"/>
+      <c r="GWD25" s="21"/>
+      <c r="GWH25" s="21"/>
+      <c r="GWL25" s="21"/>
+      <c r="GWP25" s="21"/>
+      <c r="GWT25" s="21"/>
+      <c r="GWX25" s="21"/>
+      <c r="GXB25" s="21"/>
+      <c r="GXF25" s="21"/>
+      <c r="GXJ25" s="21"/>
+      <c r="GXN25" s="21"/>
+      <c r="GXR25" s="21"/>
+      <c r="GXV25" s="21"/>
+      <c r="GXZ25" s="21"/>
+      <c r="GYD25" s="21"/>
+      <c r="GYH25" s="21"/>
+      <c r="GYL25" s="21"/>
+      <c r="GYP25" s="21"/>
+      <c r="GYT25" s="21"/>
+      <c r="GYX25" s="21"/>
+      <c r="GZB25" s="21"/>
+      <c r="GZF25" s="21"/>
+      <c r="GZJ25" s="21"/>
+      <c r="GZN25" s="21"/>
+      <c r="GZR25" s="21"/>
+      <c r="GZV25" s="21"/>
+      <c r="GZZ25" s="21"/>
+      <c r="HAD25" s="21"/>
+      <c r="HAH25" s="21"/>
+      <c r="HAL25" s="21"/>
+      <c r="HAP25" s="21"/>
+      <c r="HAT25" s="21"/>
+      <c r="HAX25" s="21"/>
+      <c r="HBB25" s="21"/>
+      <c r="HBF25" s="21"/>
+      <c r="HBJ25" s="21"/>
+      <c r="HBN25" s="21"/>
+      <c r="HBR25" s="21"/>
+      <c r="HBV25" s="21"/>
+      <c r="HBZ25" s="21"/>
+      <c r="HCD25" s="21"/>
+      <c r="HCH25" s="21"/>
+      <c r="HCL25" s="21"/>
+      <c r="HCP25" s="21"/>
+      <c r="HCT25" s="21"/>
+      <c r="HCX25" s="21"/>
+      <c r="HDB25" s="21"/>
+      <c r="HDF25" s="21"/>
+      <c r="HDJ25" s="21"/>
+      <c r="HDN25" s="21"/>
+      <c r="HDR25" s="21"/>
+      <c r="HDV25" s="21"/>
+      <c r="HDZ25" s="21"/>
+      <c r="HED25" s="21"/>
+      <c r="HEH25" s="21"/>
+      <c r="HEL25" s="21"/>
+      <c r="HEP25" s="21"/>
+      <c r="HET25" s="21"/>
+      <c r="HEX25" s="21"/>
+      <c r="HFB25" s="21"/>
+      <c r="HFF25" s="21"/>
+      <c r="HFJ25" s="21"/>
+      <c r="HFN25" s="21"/>
+      <c r="HFR25" s="21"/>
+      <c r="HFV25" s="21"/>
+      <c r="HFZ25" s="21"/>
+      <c r="HGD25" s="21"/>
+      <c r="HGH25" s="21"/>
+      <c r="HGL25" s="21"/>
+      <c r="HGP25" s="21"/>
+      <c r="HGT25" s="21"/>
+      <c r="HGX25" s="21"/>
+      <c r="HHB25" s="21"/>
+      <c r="HHF25" s="21"/>
+      <c r="HHJ25" s="21"/>
+      <c r="HHN25" s="21"/>
+      <c r="HHR25" s="21"/>
+      <c r="HHV25" s="21"/>
+      <c r="HHZ25" s="21"/>
+      <c r="HID25" s="21"/>
+      <c r="HIH25" s="21"/>
+      <c r="HIL25" s="21"/>
+      <c r="HIP25" s="21"/>
+      <c r="HIT25" s="21"/>
+      <c r="HIX25" s="21"/>
+      <c r="HJB25" s="21"/>
+      <c r="HJF25" s="21"/>
+      <c r="HJJ25" s="21"/>
+      <c r="HJN25" s="21"/>
+      <c r="HJR25" s="21"/>
+      <c r="HJV25" s="21"/>
+      <c r="HJZ25" s="21"/>
+      <c r="HKD25" s="21"/>
+      <c r="HKH25" s="21"/>
+      <c r="HKL25" s="21"/>
+      <c r="HKP25" s="21"/>
+      <c r="HKT25" s="21"/>
+      <c r="HKX25" s="21"/>
+      <c r="HLB25" s="21"/>
+      <c r="HLF25" s="21"/>
+      <c r="HLJ25" s="21"/>
+      <c r="HLN25" s="21"/>
+      <c r="HLR25" s="21"/>
+      <c r="HLV25" s="21"/>
+      <c r="HLZ25" s="21"/>
+      <c r="HMD25" s="21"/>
+      <c r="HMH25" s="21"/>
+      <c r="HML25" s="21"/>
+      <c r="HMP25" s="21"/>
+      <c r="HMT25" s="21"/>
+      <c r="HMX25" s="21"/>
+      <c r="HNB25" s="21"/>
+      <c r="HNF25" s="21"/>
+      <c r="HNJ25" s="21"/>
+      <c r="HNN25" s="21"/>
+      <c r="HNR25" s="21"/>
+      <c r="HNV25" s="21"/>
+      <c r="HNZ25" s="21"/>
+      <c r="HOD25" s="21"/>
+      <c r="HOH25" s="21"/>
+      <c r="HOL25" s="21"/>
+      <c r="HOP25" s="21"/>
+      <c r="HOT25" s="21"/>
+      <c r="HOX25" s="21"/>
+      <c r="HPB25" s="21"/>
+      <c r="HPF25" s="21"/>
+      <c r="HPJ25" s="21"/>
+      <c r="HPN25" s="21"/>
+      <c r="HPR25" s="21"/>
+      <c r="HPV25" s="21"/>
+      <c r="HPZ25" s="21"/>
+      <c r="HQD25" s="21"/>
+      <c r="HQH25" s="21"/>
+      <c r="HQL25" s="21"/>
+      <c r="HQP25" s="21"/>
+      <c r="HQT25" s="21"/>
+      <c r="HQX25" s="21"/>
+      <c r="HRB25" s="21"/>
+      <c r="HRF25" s="21"/>
+      <c r="HRJ25" s="21"/>
+      <c r="HRN25" s="21"/>
+      <c r="HRR25" s="21"/>
+      <c r="HRV25" s="21"/>
+      <c r="HRZ25" s="21"/>
+      <c r="HSD25" s="21"/>
+      <c r="HSH25" s="21"/>
+      <c r="HSL25" s="21"/>
+      <c r="HSP25" s="21"/>
+      <c r="HST25" s="21"/>
+      <c r="HSX25" s="21"/>
+      <c r="HTB25" s="21"/>
+      <c r="HTF25" s="21"/>
+      <c r="HTJ25" s="21"/>
+      <c r="HTN25" s="21"/>
+      <c r="HTR25" s="21"/>
+      <c r="HTV25" s="21"/>
+      <c r="HTZ25" s="21"/>
+      <c r="HUD25" s="21"/>
+      <c r="HUH25" s="21"/>
+      <c r="HUL25" s="21"/>
+      <c r="HUP25" s="21"/>
+      <c r="HUT25" s="21"/>
+      <c r="HUX25" s="21"/>
+      <c r="HVB25" s="21"/>
+      <c r="HVF25" s="21"/>
+      <c r="HVJ25" s="21"/>
+      <c r="HVN25" s="21"/>
+      <c r="HVR25" s="21"/>
+      <c r="HVV25" s="21"/>
+      <c r="HVZ25" s="21"/>
+      <c r="HWD25" s="21"/>
+      <c r="HWH25" s="21"/>
+      <c r="HWL25" s="21"/>
+      <c r="HWP25" s="21"/>
+      <c r="HWT25" s="21"/>
+      <c r="HWX25" s="21"/>
+      <c r="HXB25" s="21"/>
+      <c r="HXF25" s="21"/>
+      <c r="HXJ25" s="21"/>
+      <c r="HXN25" s="21"/>
+      <c r="HXR25" s="21"/>
+      <c r="HXV25" s="21"/>
+      <c r="HXZ25" s="21"/>
+      <c r="HYD25" s="21"/>
+      <c r="HYH25" s="21"/>
+      <c r="HYL25" s="21"/>
+      <c r="HYP25" s="21"/>
+      <c r="HYT25" s="21"/>
+      <c r="HYX25" s="21"/>
+      <c r="HZB25" s="21"/>
+      <c r="HZF25" s="21"/>
+      <c r="HZJ25" s="21"/>
+      <c r="HZN25" s="21"/>
+      <c r="HZR25" s="21"/>
+      <c r="HZV25" s="21"/>
+      <c r="HZZ25" s="21"/>
+      <c r="IAD25" s="21"/>
+      <c r="IAH25" s="21"/>
+      <c r="IAL25" s="21"/>
+      <c r="IAP25" s="21"/>
+      <c r="IAT25" s="21"/>
+      <c r="IAX25" s="21"/>
+      <c r="IBB25" s="21"/>
+      <c r="IBF25" s="21"/>
+      <c r="IBJ25" s="21"/>
+      <c r="IBN25" s="21"/>
+      <c r="IBR25" s="21"/>
+      <c r="IBV25" s="21"/>
+      <c r="IBZ25" s="21"/>
+      <c r="ICD25" s="21"/>
+      <c r="ICH25" s="21"/>
+      <c r="ICL25" s="21"/>
+      <c r="ICP25" s="21"/>
+      <c r="ICT25" s="21"/>
+      <c r="ICX25" s="21"/>
+      <c r="IDB25" s="21"/>
+      <c r="IDF25" s="21"/>
+      <c r="IDJ25" s="21"/>
+      <c r="IDN25" s="21"/>
+      <c r="IDR25" s="21"/>
+      <c r="IDV25" s="21"/>
+      <c r="IDZ25" s="21"/>
+      <c r="IED25" s="21"/>
+      <c r="IEH25" s="21"/>
+      <c r="IEL25" s="21"/>
+      <c r="IEP25" s="21"/>
+      <c r="IET25" s="21"/>
+      <c r="IEX25" s="21"/>
+      <c r="IFB25" s="21"/>
+      <c r="IFF25" s="21"/>
+      <c r="IFJ25" s="21"/>
+      <c r="IFN25" s="21"/>
+      <c r="IFR25" s="21"/>
+      <c r="IFV25" s="21"/>
+      <c r="IFZ25" s="21"/>
+      <c r="IGD25" s="21"/>
+      <c r="IGH25" s="21"/>
+      <c r="IGL25" s="21"/>
+      <c r="IGP25" s="21"/>
+      <c r="IGT25" s="21"/>
+      <c r="IGX25" s="21"/>
+      <c r="IHB25" s="21"/>
+      <c r="IHF25" s="21"/>
+      <c r="IHJ25" s="21"/>
+      <c r="IHN25" s="21"/>
+      <c r="IHR25" s="21"/>
+      <c r="IHV25" s="21"/>
+      <c r="IHZ25" s="21"/>
+      <c r="IID25" s="21"/>
+      <c r="IIH25" s="21"/>
+      <c r="IIL25" s="21"/>
+      <c r="IIP25" s="21"/>
+      <c r="IIT25" s="21"/>
+      <c r="IIX25" s="21"/>
+      <c r="IJB25" s="21"/>
+      <c r="IJF25" s="21"/>
+      <c r="IJJ25" s="21"/>
+      <c r="IJN25" s="21"/>
+      <c r="IJR25" s="21"/>
+      <c r="IJV25" s="21"/>
+      <c r="IJZ25" s="21"/>
+      <c r="IKD25" s="21"/>
+      <c r="IKH25" s="21"/>
+      <c r="IKL25" s="21"/>
+      <c r="IKP25" s="21"/>
+      <c r="IKT25" s="21"/>
+      <c r="IKX25" s="21"/>
+      <c r="ILB25" s="21"/>
+      <c r="ILF25" s="21"/>
+      <c r="ILJ25" s="21"/>
+      <c r="ILN25" s="21"/>
+      <c r="ILR25" s="21"/>
+      <c r="ILV25" s="21"/>
+      <c r="ILZ25" s="21"/>
+      <c r="IMD25" s="21"/>
+      <c r="IMH25" s="21"/>
+      <c r="IML25" s="21"/>
+      <c r="IMP25" s="21"/>
+      <c r="IMT25" s="21"/>
+      <c r="IMX25" s="21"/>
+      <c r="INB25" s="21"/>
+      <c r="INF25" s="21"/>
+      <c r="INJ25" s="21"/>
+      <c r="INN25" s="21"/>
+      <c r="INR25" s="21"/>
+      <c r="INV25" s="21"/>
+      <c r="INZ25" s="21"/>
+      <c r="IOD25" s="21"/>
+      <c r="IOH25" s="21"/>
+      <c r="IOL25" s="21"/>
+      <c r="IOP25" s="21"/>
+      <c r="IOT25" s="21"/>
+      <c r="IOX25" s="21"/>
+      <c r="IPB25" s="21"/>
+      <c r="IPF25" s="21"/>
+      <c r="IPJ25" s="21"/>
+      <c r="IPN25" s="21"/>
+      <c r="IPR25" s="21"/>
+      <c r="IPV25" s="21"/>
+      <c r="IPZ25" s="21"/>
+      <c r="IQD25" s="21"/>
+      <c r="IQH25" s="21"/>
+      <c r="IQL25" s="21"/>
+      <c r="IQP25" s="21"/>
+      <c r="IQT25" s="21"/>
+      <c r="IQX25" s="21"/>
+      <c r="IRB25" s="21"/>
+      <c r="IRF25" s="21"/>
+      <c r="IRJ25" s="21"/>
+      <c r="IRN25" s="21"/>
+      <c r="IRR25" s="21"/>
+      <c r="IRV25" s="21"/>
+      <c r="IRZ25" s="21"/>
+      <c r="ISD25" s="21"/>
+      <c r="ISH25" s="21"/>
+      <c r="ISL25" s="21"/>
+      <c r="ISP25" s="21"/>
+      <c r="IST25" s="21"/>
+      <c r="ISX25" s="21"/>
+      <c r="ITB25" s="21"/>
+      <c r="ITF25" s="21"/>
+      <c r="ITJ25" s="21"/>
+      <c r="ITN25" s="21"/>
+      <c r="ITR25" s="21"/>
+      <c r="ITV25" s="21"/>
+      <c r="ITZ25" s="21"/>
+      <c r="IUD25" s="21"/>
+      <c r="IUH25" s="21"/>
+      <c r="IUL25" s="21"/>
+      <c r="IUP25" s="21"/>
+      <c r="IUT25" s="21"/>
+      <c r="IUX25" s="21"/>
+      <c r="IVB25" s="21"/>
+      <c r="IVF25" s="21"/>
+      <c r="IVJ25" s="21"/>
+      <c r="IVN25" s="21"/>
+      <c r="IVR25" s="21"/>
+      <c r="IVV25" s="21"/>
+      <c r="IVZ25" s="21"/>
+      <c r="IWD25" s="21"/>
+      <c r="IWH25" s="21"/>
+      <c r="IWL25" s="21"/>
+      <c r="IWP25" s="21"/>
+      <c r="IWT25" s="21"/>
+      <c r="IWX25" s="21"/>
+      <c r="IXB25" s="21"/>
+      <c r="IXF25" s="21"/>
+      <c r="IXJ25" s="21"/>
+      <c r="IXN25" s="21"/>
+      <c r="IXR25" s="21"/>
+      <c r="IXV25" s="21"/>
+      <c r="IXZ25" s="21"/>
+      <c r="IYD25" s="21"/>
+      <c r="IYH25" s="21"/>
+      <c r="IYL25" s="21"/>
+      <c r="IYP25" s="21"/>
+      <c r="IYT25" s="21"/>
+      <c r="IYX25" s="21"/>
+      <c r="IZB25" s="21"/>
+      <c r="IZF25" s="21"/>
+      <c r="IZJ25" s="21"/>
+      <c r="IZN25" s="21"/>
+      <c r="IZR25" s="21"/>
+      <c r="IZV25" s="21"/>
+      <c r="IZZ25" s="21"/>
+      <c r="JAD25" s="21"/>
+      <c r="JAH25" s="21"/>
+      <c r="JAL25" s="21"/>
+      <c r="JAP25" s="21"/>
+      <c r="JAT25" s="21"/>
+      <c r="JAX25" s="21"/>
+      <c r="JBB25" s="21"/>
+      <c r="JBF25" s="21"/>
+      <c r="JBJ25" s="21"/>
+      <c r="JBN25" s="21"/>
+      <c r="JBR25" s="21"/>
+      <c r="JBV25" s="21"/>
+      <c r="JBZ25" s="21"/>
+      <c r="JCD25" s="21"/>
+      <c r="JCH25" s="21"/>
+      <c r="JCL25" s="21"/>
+      <c r="JCP25" s="21"/>
+      <c r="JCT25" s="21"/>
+      <c r="JCX25" s="21"/>
+      <c r="JDB25" s="21"/>
+      <c r="JDF25" s="21"/>
+      <c r="JDJ25" s="21"/>
+      <c r="JDN25" s="21"/>
+      <c r="JDR25" s="21"/>
+      <c r="JDV25" s="21"/>
+      <c r="JDZ25" s="21"/>
+      <c r="JED25" s="21"/>
+      <c r="JEH25" s="21"/>
+      <c r="JEL25" s="21"/>
+      <c r="JEP25" s="21"/>
+      <c r="JET25" s="21"/>
+      <c r="JEX25" s="21"/>
+      <c r="JFB25" s="21"/>
+      <c r="JFF25" s="21"/>
+      <c r="JFJ25" s="21"/>
+      <c r="JFN25" s="21"/>
+      <c r="JFR25" s="21"/>
+      <c r="JFV25" s="21"/>
+      <c r="JFZ25" s="21"/>
+      <c r="JGD25" s="21"/>
+      <c r="JGH25" s="21"/>
+      <c r="JGL25" s="21"/>
+      <c r="JGP25" s="21"/>
+      <c r="JGT25" s="21"/>
+      <c r="JGX25" s="21"/>
+      <c r="JHB25" s="21"/>
+      <c r="JHF25" s="21"/>
+      <c r="JHJ25" s="21"/>
+      <c r="JHN25" s="21"/>
+      <c r="JHR25" s="21"/>
+      <c r="JHV25" s="21"/>
+      <c r="JHZ25" s="21"/>
+      <c r="JID25" s="21"/>
+      <c r="JIH25" s="21"/>
+      <c r="JIL25" s="21"/>
+      <c r="JIP25" s="21"/>
+      <c r="JIT25" s="21"/>
+      <c r="JIX25" s="21"/>
+      <c r="JJB25" s="21"/>
+      <c r="JJF25" s="21"/>
+      <c r="JJJ25" s="21"/>
+      <c r="JJN25" s="21"/>
+      <c r="JJR25" s="21"/>
+      <c r="JJV25" s="21"/>
+      <c r="JJZ25" s="21"/>
+      <c r="JKD25" s="21"/>
+      <c r="JKH25" s="21"/>
+      <c r="JKL25" s="21"/>
+      <c r="JKP25" s="21"/>
+      <c r="JKT25" s="21"/>
+      <c r="JKX25" s="21"/>
+      <c r="JLB25" s="21"/>
+      <c r="JLF25" s="21"/>
+      <c r="JLJ25" s="21"/>
+      <c r="JLN25" s="21"/>
+      <c r="JLR25" s="21"/>
+      <c r="JLV25" s="21"/>
+      <c r="JLZ25" s="21"/>
+      <c r="JMD25" s="21"/>
+      <c r="JMH25" s="21"/>
+      <c r="JML25" s="21"/>
+      <c r="JMP25" s="21"/>
+      <c r="JMT25" s="21"/>
+      <c r="JMX25" s="21"/>
+      <c r="JNB25" s="21"/>
+      <c r="JNF25" s="21"/>
+      <c r="JNJ25" s="21"/>
+      <c r="JNN25" s="21"/>
+      <c r="JNR25" s="21"/>
+      <c r="JNV25" s="21"/>
+      <c r="JNZ25" s="21"/>
+      <c r="JOD25" s="21"/>
+      <c r="JOH25" s="21"/>
+      <c r="JOL25" s="21"/>
+      <c r="JOP25" s="21"/>
+      <c r="JOT25" s="21"/>
+      <c r="JOX25" s="21"/>
+      <c r="JPB25" s="21"/>
+      <c r="JPF25" s="21"/>
+      <c r="JPJ25" s="21"/>
+      <c r="JPN25" s="21"/>
+      <c r="JPR25" s="21"/>
+      <c r="JPV25" s="21"/>
+      <c r="JPZ25" s="21"/>
+      <c r="JQD25" s="21"/>
+      <c r="JQH25" s="21"/>
+      <c r="JQL25" s="21"/>
+      <c r="JQP25" s="21"/>
+      <c r="JQT25" s="21"/>
+      <c r="JQX25" s="21"/>
+      <c r="JRB25" s="21"/>
+      <c r="JRF25" s="21"/>
+      <c r="JRJ25" s="21"/>
+      <c r="JRN25" s="21"/>
+      <c r="JRR25" s="21"/>
+      <c r="JRV25" s="21"/>
+      <c r="JRZ25" s="21"/>
+      <c r="JSD25" s="21"/>
+      <c r="JSH25" s="21"/>
+      <c r="JSL25" s="21"/>
+      <c r="JSP25" s="21"/>
+      <c r="JST25" s="21"/>
+      <c r="JSX25" s="21"/>
+      <c r="JTB25" s="21"/>
+      <c r="JTF25" s="21"/>
+      <c r="JTJ25" s="21"/>
+      <c r="JTN25" s="21"/>
+      <c r="JTR25" s="21"/>
+      <c r="JTV25" s="21"/>
+      <c r="JTZ25" s="21"/>
+      <c r="JUD25" s="21"/>
+      <c r="JUH25" s="21"/>
+      <c r="JUL25" s="21"/>
+      <c r="JUP25" s="21"/>
+      <c r="JUT25" s="21"/>
+      <c r="JUX25" s="21"/>
+      <c r="JVB25" s="21"/>
+      <c r="JVF25" s="21"/>
+      <c r="JVJ25" s="21"/>
+      <c r="JVN25" s="21"/>
+      <c r="JVR25" s="21"/>
+      <c r="JVV25" s="21"/>
+      <c r="JVZ25" s="21"/>
+      <c r="JWD25" s="21"/>
+      <c r="JWH25" s="21"/>
+      <c r="JWL25" s="21"/>
+      <c r="JWP25" s="21"/>
+      <c r="JWT25" s="21"/>
+      <c r="JWX25" s="21"/>
+      <c r="JXB25" s="21"/>
+      <c r="JXF25" s="21"/>
+      <c r="JXJ25" s="21"/>
+      <c r="JXN25" s="21"/>
+      <c r="JXR25" s="21"/>
+      <c r="JXV25" s="21"/>
+      <c r="JXZ25" s="21"/>
+      <c r="JYD25" s="21"/>
+      <c r="JYH25" s="21"/>
+      <c r="JYL25" s="21"/>
+      <c r="JYP25" s="21"/>
+      <c r="JYT25" s="21"/>
+      <c r="JYX25" s="21"/>
+      <c r="JZB25" s="21"/>
+      <c r="JZF25" s="21"/>
+      <c r="JZJ25" s="21"/>
+      <c r="JZN25" s="21"/>
+      <c r="JZR25" s="21"/>
+      <c r="JZV25" s="21"/>
+      <c r="JZZ25" s="21"/>
+      <c r="KAD25" s="21"/>
+      <c r="KAH25" s="21"/>
+      <c r="KAL25" s="21"/>
+      <c r="KAP25" s="21"/>
+      <c r="KAT25" s="21"/>
+      <c r="KAX25" s="21"/>
+      <c r="KBB25" s="21"/>
+      <c r="KBF25" s="21"/>
+      <c r="KBJ25" s="21"/>
+      <c r="KBN25" s="21"/>
+      <c r="KBR25" s="21"/>
+      <c r="KBV25" s="21"/>
+      <c r="KBZ25" s="21"/>
+      <c r="KCD25" s="21"/>
+      <c r="KCH25" s="21"/>
+      <c r="KCL25" s="21"/>
+      <c r="KCP25" s="21"/>
+      <c r="KCT25" s="21"/>
+      <c r="KCX25" s="21"/>
+      <c r="KDB25" s="21"/>
+      <c r="KDF25" s="21"/>
+      <c r="KDJ25" s="21"/>
+      <c r="KDN25" s="21"/>
+      <c r="KDR25" s="21"/>
+      <c r="KDV25" s="21"/>
+      <c r="KDZ25" s="21"/>
+      <c r="KED25" s="21"/>
+      <c r="KEH25" s="21"/>
+      <c r="KEL25" s="21"/>
+      <c r="KEP25" s="21"/>
+      <c r="KET25" s="21"/>
+      <c r="KEX25" s="21"/>
+      <c r="KFB25" s="21"/>
+      <c r="KFF25" s="21"/>
+      <c r="KFJ25" s="21"/>
+      <c r="KFN25" s="21"/>
+      <c r="KFR25" s="21"/>
+      <c r="KFV25" s="21"/>
+      <c r="KFZ25" s="21"/>
+      <c r="KGD25" s="21"/>
+      <c r="KGH25" s="21"/>
+      <c r="KGL25" s="21"/>
+      <c r="KGP25" s="21"/>
+      <c r="KGT25" s="21"/>
+      <c r="KGX25" s="21"/>
+      <c r="KHB25" s="21"/>
+      <c r="KHF25" s="21"/>
+      <c r="KHJ25" s="21"/>
+      <c r="KHN25" s="21"/>
+      <c r="KHR25" s="21"/>
+      <c r="KHV25" s="21"/>
+      <c r="KHZ25" s="21"/>
+      <c r="KID25" s="21"/>
+      <c r="KIH25" s="21"/>
+      <c r="KIL25" s="21"/>
+      <c r="KIP25" s="21"/>
+      <c r="KIT25" s="21"/>
+      <c r="KIX25" s="21"/>
+      <c r="KJB25" s="21"/>
+      <c r="KJF25" s="21"/>
+      <c r="KJJ25" s="21"/>
+      <c r="KJN25" s="21"/>
+      <c r="KJR25" s="21"/>
+      <c r="KJV25" s="21"/>
+      <c r="KJZ25" s="21"/>
+      <c r="KKD25" s="21"/>
+      <c r="KKH25" s="21"/>
+      <c r="KKL25" s="21"/>
+      <c r="KKP25" s="21"/>
+      <c r="KKT25" s="21"/>
+      <c r="KKX25" s="21"/>
+      <c r="KLB25" s="21"/>
+      <c r="KLF25" s="21"/>
+      <c r="KLJ25" s="21"/>
+      <c r="KLN25" s="21"/>
+      <c r="KLR25" s="21"/>
+      <c r="KLV25" s="21"/>
+      <c r="KLZ25" s="21"/>
+      <c r="KMD25" s="21"/>
+      <c r="KMH25" s="21"/>
+      <c r="KML25" s="21"/>
+      <c r="KMP25" s="21"/>
+      <c r="KMT25" s="21"/>
+      <c r="KMX25" s="21"/>
+      <c r="KNB25" s="21"/>
+      <c r="KNF25" s="21"/>
+      <c r="KNJ25" s="21"/>
+      <c r="KNN25" s="21"/>
+      <c r="KNR25" s="21"/>
+      <c r="KNV25" s="21"/>
+      <c r="KNZ25" s="21"/>
+      <c r="KOD25" s="21"/>
+      <c r="KOH25" s="21"/>
+      <c r="KOL25" s="21"/>
+      <c r="KOP25" s="21"/>
+      <c r="KOT25" s="21"/>
+      <c r="KOX25" s="21"/>
+      <c r="KPB25" s="21"/>
+      <c r="KPF25" s="21"/>
+      <c r="KPJ25" s="21"/>
+      <c r="KPN25" s="21"/>
+      <c r="KPR25" s="21"/>
+      <c r="KPV25" s="21"/>
+      <c r="KPZ25" s="21"/>
+      <c r="KQD25" s="21"/>
+      <c r="KQH25" s="21"/>
+      <c r="KQL25" s="21"/>
+      <c r="KQP25" s="21"/>
+      <c r="KQT25" s="21"/>
+      <c r="KQX25" s="21"/>
+      <c r="KRB25" s="21"/>
+      <c r="KRF25" s="21"/>
+      <c r="KRJ25" s="21"/>
+      <c r="KRN25" s="21"/>
+      <c r="KRR25" s="21"/>
+      <c r="KRV25" s="21"/>
+      <c r="KRZ25" s="21"/>
+      <c r="KSD25" s="21"/>
+      <c r="KSH25" s="21"/>
+      <c r="KSL25" s="21"/>
+      <c r="KSP25" s="21"/>
+      <c r="KST25" s="21"/>
+      <c r="KSX25" s="21"/>
+      <c r="KTB25" s="21"/>
+      <c r="KTF25" s="21"/>
+      <c r="KTJ25" s="21"/>
+      <c r="KTN25" s="21"/>
+      <c r="KTR25" s="21"/>
+      <c r="KTV25" s="21"/>
+      <c r="KTZ25" s="21"/>
+      <c r="KUD25" s="21"/>
+      <c r="KUH25" s="21"/>
+      <c r="KUL25" s="21"/>
+      <c r="KUP25" s="21"/>
+      <c r="KUT25" s="21"/>
+      <c r="KUX25" s="21"/>
+      <c r="KVB25" s="21"/>
+      <c r="KVF25" s="21"/>
+      <c r="KVJ25" s="21"/>
+      <c r="KVN25" s="21"/>
+      <c r="KVR25" s="21"/>
+      <c r="KVV25" s="21"/>
+      <c r="KVZ25" s="21"/>
+      <c r="KWD25" s="21"/>
+      <c r="KWH25" s="21"/>
+      <c r="KWL25" s="21"/>
+      <c r="KWP25" s="21"/>
+      <c r="KWT25" s="21"/>
+      <c r="KWX25" s="21"/>
+      <c r="KXB25" s="21"/>
+      <c r="KXF25" s="21"/>
+      <c r="KXJ25" s="21"/>
+      <c r="KXN25" s="21"/>
+      <c r="KXR25" s="21"/>
+      <c r="KXV25" s="21"/>
+      <c r="KXZ25" s="21"/>
+      <c r="KYD25" s="21"/>
+      <c r="KYH25" s="21"/>
+      <c r="KYL25" s="21"/>
+      <c r="KYP25" s="21"/>
+      <c r="KYT25" s="21"/>
+      <c r="KYX25" s="21"/>
+      <c r="KZB25" s="21"/>
+      <c r="KZF25" s="21"/>
+      <c r="KZJ25" s="21"/>
+      <c r="KZN25" s="21"/>
+      <c r="KZR25" s="21"/>
+      <c r="KZV25" s="21"/>
+      <c r="KZZ25" s="21"/>
+      <c r="LAD25" s="21"/>
+      <c r="LAH25" s="21"/>
+      <c r="LAL25" s="21"/>
+      <c r="LAP25" s="21"/>
+      <c r="LAT25" s="21"/>
+      <c r="LAX25" s="21"/>
+      <c r="LBB25" s="21"/>
+      <c r="LBF25" s="21"/>
+      <c r="LBJ25" s="21"/>
+      <c r="LBN25" s="21"/>
+      <c r="LBR25" s="21"/>
+      <c r="LBV25" s="21"/>
+      <c r="LBZ25" s="21"/>
+      <c r="LCD25" s="21"/>
+      <c r="LCH25" s="21"/>
+      <c r="LCL25" s="21"/>
+      <c r="LCP25" s="21"/>
+      <c r="LCT25" s="21"/>
+      <c r="LCX25" s="21"/>
+      <c r="LDB25" s="21"/>
+      <c r="LDF25" s="21"/>
+      <c r="LDJ25" s="21"/>
+      <c r="LDN25" s="21"/>
+      <c r="LDR25" s="21"/>
+      <c r="LDV25" s="21"/>
+      <c r="LDZ25" s="21"/>
+      <c r="LED25" s="21"/>
+      <c r="LEH25" s="21"/>
+      <c r="LEL25" s="21"/>
+      <c r="LEP25" s="21"/>
+      <c r="LET25" s="21"/>
+      <c r="LEX25" s="21"/>
+      <c r="LFB25" s="21"/>
+      <c r="LFF25" s="21"/>
+      <c r="LFJ25" s="21"/>
+      <c r="LFN25" s="21"/>
+      <c r="LFR25" s="21"/>
+      <c r="LFV25" s="21"/>
+      <c r="LFZ25" s="21"/>
+      <c r="LGD25" s="21"/>
+      <c r="LGH25" s="21"/>
+      <c r="LGL25" s="21"/>
+      <c r="LGP25" s="21"/>
+      <c r="LGT25" s="21"/>
+      <c r="LGX25" s="21"/>
+      <c r="LHB25" s="21"/>
+      <c r="LHF25" s="21"/>
+      <c r="LHJ25" s="21"/>
+      <c r="LHN25" s="21"/>
+      <c r="LHR25" s="21"/>
+      <c r="LHV25" s="21"/>
+      <c r="LHZ25" s="21"/>
+      <c r="LID25" s="21"/>
+      <c r="LIH25" s="21"/>
+      <c r="LIL25" s="21"/>
+      <c r="LIP25" s="21"/>
+      <c r="LIT25" s="21"/>
+      <c r="LIX25" s="21"/>
+      <c r="LJB25" s="21"/>
+      <c r="LJF25" s="21"/>
+      <c r="LJJ25" s="21"/>
+      <c r="LJN25" s="21"/>
+      <c r="LJR25" s="21"/>
+      <c r="LJV25" s="21"/>
+      <c r="LJZ25" s="21"/>
+      <c r="LKD25" s="21"/>
+      <c r="LKH25" s="21"/>
+      <c r="LKL25" s="21"/>
+      <c r="LKP25" s="21"/>
+      <c r="LKT25" s="21"/>
+      <c r="LKX25" s="21"/>
+      <c r="LLB25" s="21"/>
+      <c r="LLF25" s="21"/>
+      <c r="LLJ25" s="21"/>
+      <c r="LLN25" s="21"/>
+      <c r="LLR25" s="21"/>
+      <c r="LLV25" s="21"/>
+      <c r="LLZ25" s="21"/>
+      <c r="LMD25" s="21"/>
+      <c r="LMH25" s="21"/>
+      <c r="LML25" s="21"/>
+      <c r="LMP25" s="21"/>
+      <c r="LMT25" s="21"/>
+      <c r="LMX25" s="21"/>
+      <c r="LNB25" s="21"/>
+      <c r="LNF25" s="21"/>
+      <c r="LNJ25" s="21"/>
+      <c r="LNN25" s="21"/>
+      <c r="LNR25" s="21"/>
+      <c r="LNV25" s="21"/>
+      <c r="LNZ25" s="21"/>
+      <c r="LOD25" s="21"/>
+      <c r="LOH25" s="21"/>
+      <c r="LOL25" s="21"/>
+      <c r="LOP25" s="21"/>
+      <c r="LOT25" s="21"/>
+      <c r="LOX25" s="21"/>
+      <c r="LPB25" s="21"/>
+      <c r="LPF25" s="21"/>
+      <c r="LPJ25" s="21"/>
+      <c r="LPN25" s="21"/>
+      <c r="LPR25" s="21"/>
+      <c r="LPV25" s="21"/>
+      <c r="LPZ25" s="21"/>
+      <c r="LQD25" s="21"/>
+      <c r="LQH25" s="21"/>
+      <c r="LQL25" s="21"/>
+      <c r="LQP25" s="21"/>
+      <c r="LQT25" s="21"/>
+      <c r="LQX25" s="21"/>
+      <c r="LRB25" s="21"/>
+      <c r="LRF25" s="21"/>
+      <c r="LRJ25" s="21"/>
+      <c r="LRN25" s="21"/>
+      <c r="LRR25" s="21"/>
+      <c r="LRV25" s="21"/>
+      <c r="LRZ25" s="21"/>
+      <c r="LSD25" s="21"/>
+      <c r="LSH25" s="21"/>
+      <c r="LSL25" s="21"/>
+      <c r="LSP25" s="21"/>
+      <c r="LST25" s="21"/>
+      <c r="LSX25" s="21"/>
+      <c r="LTB25" s="21"/>
+      <c r="LTF25" s="21"/>
+      <c r="LTJ25" s="21"/>
+      <c r="LTN25" s="21"/>
+      <c r="LTR25" s="21"/>
+      <c r="LTV25" s="21"/>
+      <c r="LTZ25" s="21"/>
+      <c r="LUD25" s="21"/>
+      <c r="LUH25" s="21"/>
+      <c r="LUL25" s="21"/>
+      <c r="LUP25" s="21"/>
+      <c r="LUT25" s="21"/>
+      <c r="LUX25" s="21"/>
+      <c r="LVB25" s="21"/>
+      <c r="LVF25" s="21"/>
+      <c r="LVJ25" s="21"/>
+      <c r="LVN25" s="21"/>
+      <c r="LVR25" s="21"/>
+      <c r="LVV25" s="21"/>
+      <c r="LVZ25" s="21"/>
+      <c r="LWD25" s="21"/>
+      <c r="LWH25" s="21"/>
+      <c r="LWL25" s="21"/>
+      <c r="LWP25" s="21"/>
+      <c r="LWT25" s="21"/>
+      <c r="LWX25" s="21"/>
+      <c r="LXB25" s="21"/>
+      <c r="LXF25" s="21"/>
+      <c r="LXJ25" s="21"/>
+      <c r="LXN25" s="21"/>
+      <c r="LXR25" s="21"/>
+      <c r="LXV25" s="21"/>
+      <c r="LXZ25" s="21"/>
+      <c r="LYD25" s="21"/>
+      <c r="LYH25" s="21"/>
+      <c r="LYL25" s="21"/>
+      <c r="LYP25" s="21"/>
+      <c r="LYT25" s="21"/>
+      <c r="LYX25" s="21"/>
+      <c r="LZB25" s="21"/>
+      <c r="LZF25" s="21"/>
+      <c r="LZJ25" s="21"/>
+      <c r="LZN25" s="21"/>
+      <c r="LZR25" s="21"/>
+      <c r="LZV25" s="21"/>
+      <c r="LZZ25" s="21"/>
+      <c r="MAD25" s="21"/>
+      <c r="MAH25" s="21"/>
+      <c r="MAL25" s="21"/>
+      <c r="MAP25" s="21"/>
+      <c r="MAT25" s="21"/>
+      <c r="MAX25" s="21"/>
+      <c r="MBB25" s="21"/>
+      <c r="MBF25" s="21"/>
+      <c r="MBJ25" s="21"/>
+      <c r="MBN25" s="21"/>
+      <c r="MBR25" s="21"/>
+      <c r="MBV25" s="21"/>
+      <c r="MBZ25" s="21"/>
+      <c r="MCD25" s="21"/>
+      <c r="MCH25" s="21"/>
+      <c r="MCL25" s="21"/>
+      <c r="MCP25" s="21"/>
+      <c r="MCT25" s="21"/>
+      <c r="MCX25" s="21"/>
+      <c r="MDB25" s="21"/>
+      <c r="MDF25" s="21"/>
+      <c r="MDJ25" s="21"/>
+      <c r="MDN25" s="21"/>
+      <c r="MDR25" s="21"/>
+      <c r="MDV25" s="21"/>
+      <c r="MDZ25" s="21"/>
+      <c r="MED25" s="21"/>
+      <c r="MEH25" s="21"/>
+      <c r="MEL25" s="21"/>
+      <c r="MEP25" s="21"/>
+      <c r="MET25" s="21"/>
+      <c r="MEX25" s="21"/>
+      <c r="MFB25" s="21"/>
+      <c r="MFF25" s="21"/>
+      <c r="MFJ25" s="21"/>
+      <c r="MFN25" s="21"/>
+      <c r="MFR25" s="21"/>
+      <c r="MFV25" s="21"/>
+      <c r="MFZ25" s="21"/>
+      <c r="MGD25" s="21"/>
+      <c r="MGH25" s="21"/>
+      <c r="MGL25" s="21"/>
+      <c r="MGP25" s="21"/>
+      <c r="MGT25" s="21"/>
+      <c r="MGX25" s="21"/>
+      <c r="MHB25" s="21"/>
+      <c r="MHF25" s="21"/>
+      <c r="MHJ25" s="21"/>
+      <c r="MHN25" s="21"/>
+      <c r="MHR25" s="21"/>
+      <c r="MHV25" s="21"/>
+      <c r="MHZ25" s="21"/>
+      <c r="MID25" s="21"/>
+      <c r="MIH25" s="21"/>
+      <c r="MIL25" s="21"/>
+      <c r="MIP25" s="21"/>
+      <c r="MIT25" s="21"/>
+      <c r="MIX25" s="21"/>
+      <c r="MJB25" s="21"/>
+      <c r="MJF25" s="21"/>
+      <c r="MJJ25" s="21"/>
+      <c r="MJN25" s="21"/>
+      <c r="MJR25" s="21"/>
+      <c r="MJV25" s="21"/>
+      <c r="MJZ25" s="21"/>
+      <c r="MKD25" s="21"/>
+      <c r="MKH25" s="21"/>
+      <c r="MKL25" s="21"/>
+      <c r="MKP25" s="21"/>
+      <c r="MKT25" s="21"/>
+      <c r="MKX25" s="21"/>
+      <c r="MLB25" s="21"/>
+      <c r="MLF25" s="21"/>
+      <c r="MLJ25" s="21"/>
+      <c r="MLN25" s="21"/>
+      <c r="MLR25" s="21"/>
+      <c r="MLV25" s="21"/>
+      <c r="MLZ25" s="21"/>
+      <c r="MMD25" s="21"/>
+      <c r="MMH25" s="21"/>
+      <c r="MML25" s="21"/>
+      <c r="MMP25" s="21"/>
+      <c r="MMT25" s="21"/>
+      <c r="MMX25" s="21"/>
+      <c r="MNB25" s="21"/>
+      <c r="MNF25" s="21"/>
+      <c r="MNJ25" s="21"/>
+      <c r="MNN25" s="21"/>
+      <c r="MNR25" s="21"/>
+      <c r="MNV25" s="21"/>
+      <c r="MNZ25" s="21"/>
+      <c r="MOD25" s="21"/>
+      <c r="MOH25" s="21"/>
+      <c r="MOL25" s="21"/>
+      <c r="MOP25" s="21"/>
+      <c r="MOT25" s="21"/>
+      <c r="MOX25" s="21"/>
+      <c r="MPB25" s="21"/>
+      <c r="MPF25" s="21"/>
+      <c r="MPJ25" s="21"/>
+      <c r="MPN25" s="21"/>
+      <c r="MPR25" s="21"/>
+      <c r="MPV25" s="21"/>
+      <c r="MPZ25" s="21"/>
+      <c r="MQD25" s="21"/>
+      <c r="MQH25" s="21"/>
+      <c r="MQL25" s="21"/>
+      <c r="MQP25" s="21"/>
+      <c r="MQT25" s="21"/>
+      <c r="MQX25" s="21"/>
+      <c r="MRB25" s="21"/>
+      <c r="MRF25" s="21"/>
+      <c r="MRJ25" s="21"/>
+      <c r="MRN25" s="21"/>
+      <c r="MRR25" s="21"/>
+      <c r="MRV25" s="21"/>
+      <c r="MRZ25" s="21"/>
+      <c r="MSD25" s="21"/>
+      <c r="MSH25" s="21"/>
+      <c r="MSL25" s="21"/>
+      <c r="MSP25" s="21"/>
+      <c r="MST25" s="21"/>
+      <c r="MSX25" s="21"/>
+      <c r="MTB25" s="21"/>
+      <c r="MTF25" s="21"/>
+      <c r="MTJ25" s="21"/>
+      <c r="MTN25" s="21"/>
+      <c r="MTR25" s="21"/>
+      <c r="MTV25" s="21"/>
+      <c r="MTZ25" s="21"/>
+      <c r="MUD25" s="21"/>
+      <c r="MUH25" s="21"/>
+      <c r="MUL25" s="21"/>
+      <c r="MUP25" s="21"/>
+      <c r="MUT25" s="21"/>
+      <c r="MUX25" s="21"/>
+      <c r="MVB25" s="21"/>
+      <c r="MVF25" s="21"/>
+      <c r="MVJ25" s="21"/>
+      <c r="MVN25" s="21"/>
+      <c r="MVR25" s="21"/>
+      <c r="MVV25" s="21"/>
+      <c r="MVZ25" s="21"/>
+      <c r="MWD25" s="21"/>
+      <c r="MWH25" s="21"/>
+      <c r="MWL25" s="21"/>
+      <c r="MWP25" s="21"/>
+      <c r="MWT25" s="21"/>
+      <c r="MWX25" s="21"/>
+      <c r="MXB25" s="21"/>
+      <c r="MXF25" s="21"/>
+      <c r="MXJ25" s="21"/>
+      <c r="MXN25" s="21"/>
+      <c r="MXR25" s="21"/>
+      <c r="MXV25" s="21"/>
+      <c r="MXZ25" s="21"/>
+      <c r="MYD25" s="21"/>
+      <c r="MYH25" s="21"/>
+      <c r="MYL25" s="21"/>
+      <c r="MYP25" s="21"/>
+      <c r="MYT25" s="21"/>
+      <c r="MYX25" s="21"/>
+      <c r="MZB25" s="21"/>
+      <c r="MZF25" s="21"/>
+      <c r="MZJ25" s="21"/>
+      <c r="MZN25" s="21"/>
+      <c r="MZR25" s="21"/>
+      <c r="MZV25" s="21"/>
+      <c r="MZZ25" s="21"/>
+      <c r="NAD25" s="21"/>
+      <c r="NAH25" s="21"/>
+      <c r="NAL25" s="21"/>
+      <c r="NAP25" s="21"/>
+      <c r="NAT25" s="21"/>
+      <c r="NAX25" s="21"/>
+      <c r="NBB25" s="21"/>
+      <c r="NBF25" s="21"/>
+      <c r="NBJ25" s="21"/>
+      <c r="NBN25" s="21"/>
+      <c r="NBR25" s="21"/>
+      <c r="NBV25" s="21"/>
+      <c r="NBZ25" s="21"/>
+      <c r="NCD25" s="21"/>
+      <c r="NCH25" s="21"/>
+      <c r="NCL25" s="21"/>
+      <c r="NCP25" s="21"/>
+      <c r="NCT25" s="21"/>
+      <c r="NCX25" s="21"/>
+      <c r="NDB25" s="21"/>
+      <c r="NDF25" s="21"/>
+      <c r="NDJ25" s="21"/>
+      <c r="NDN25" s="21"/>
+      <c r="NDR25" s="21"/>
+      <c r="NDV25" s="21"/>
+      <c r="NDZ25" s="21"/>
+      <c r="NED25" s="21"/>
+      <c r="NEH25" s="21"/>
+      <c r="NEL25" s="21"/>
+      <c r="NEP25" s="21"/>
+      <c r="NET25" s="21"/>
+      <c r="NEX25" s="21"/>
+      <c r="NFB25" s="21"/>
+      <c r="NFF25" s="21"/>
+      <c r="NFJ25" s="21"/>
+      <c r="NFN25" s="21"/>
+      <c r="NFR25" s="21"/>
+      <c r="NFV25" s="21"/>
+      <c r="NFZ25" s="21"/>
+      <c r="NGD25" s="21"/>
+      <c r="NGH25" s="21"/>
+      <c r="NGL25" s="21"/>
+      <c r="NGP25" s="21"/>
+      <c r="NGT25" s="21"/>
+      <c r="NGX25" s="21"/>
+      <c r="NHB25" s="21"/>
+      <c r="NHF25" s="21"/>
+      <c r="NHJ25" s="21"/>
+      <c r="NHN25" s="21"/>
+      <c r="NHR25" s="21"/>
+      <c r="NHV25" s="21"/>
+      <c r="NHZ25" s="21"/>
+      <c r="NID25" s="21"/>
+      <c r="NIH25" s="21"/>
+      <c r="NIL25" s="21"/>
+      <c r="NIP25" s="21"/>
+      <c r="NIT25" s="21"/>
+      <c r="NIX25" s="21"/>
+      <c r="NJB25" s="21"/>
+      <c r="NJF25" s="21"/>
+      <c r="NJJ25" s="21"/>
+      <c r="NJN25" s="21"/>
+      <c r="NJR25" s="21"/>
+      <c r="NJV25" s="21"/>
+      <c r="NJZ25" s="21"/>
+      <c r="NKD25" s="21"/>
+      <c r="NKH25" s="21"/>
+      <c r="NKL25" s="21"/>
+      <c r="NKP25" s="21"/>
+      <c r="NKT25" s="21"/>
+      <c r="NKX25" s="21"/>
+      <c r="NLB25" s="21"/>
+      <c r="NLF25" s="21"/>
+      <c r="NLJ25" s="21"/>
+      <c r="NLN25" s="21"/>
+      <c r="NLR25" s="21"/>
+      <c r="NLV25" s="21"/>
+      <c r="NLZ25" s="21"/>
+      <c r="NMD25" s="21"/>
+      <c r="NMH25" s="21"/>
+      <c r="NML25" s="21"/>
+      <c r="NMP25" s="21"/>
+      <c r="NMT25" s="21"/>
+      <c r="NMX25" s="21"/>
+      <c r="NNB25" s="21"/>
+      <c r="NNF25" s="21"/>
+      <c r="NNJ25" s="21"/>
+      <c r="NNN25" s="21"/>
+      <c r="NNR25" s="21"/>
+      <c r="NNV25" s="21"/>
+      <c r="NNZ25" s="21"/>
+      <c r="NOD25" s="21"/>
+      <c r="NOH25" s="21"/>
+      <c r="NOL25" s="21"/>
+      <c r="NOP25" s="21"/>
+      <c r="NOT25" s="21"/>
+      <c r="NOX25" s="21"/>
+      <c r="NPB25" s="21"/>
+      <c r="NPF25" s="21"/>
+      <c r="NPJ25" s="21"/>
+      <c r="NPN25" s="21"/>
+      <c r="NPR25" s="21"/>
+      <c r="NPV25" s="21"/>
+      <c r="NPZ25" s="21"/>
+      <c r="NQD25" s="21"/>
+      <c r="NQH25" s="21"/>
+      <c r="NQL25" s="21"/>
+      <c r="NQP25" s="21"/>
+      <c r="NQT25" s="21"/>
+      <c r="NQX25" s="21"/>
+      <c r="NRB25" s="21"/>
+      <c r="NRF25" s="21"/>
+      <c r="NRJ25" s="21"/>
+      <c r="NRN25" s="21"/>
+      <c r="NRR25" s="21"/>
+      <c r="NRV25" s="21"/>
+      <c r="NRZ25" s="21"/>
+      <c r="NSD25" s="21"/>
+      <c r="NSH25" s="21"/>
+      <c r="NSL25" s="21"/>
+      <c r="NSP25" s="21"/>
+      <c r="NST25" s="21"/>
+      <c r="NSX25" s="21"/>
+      <c r="NTB25" s="21"/>
+      <c r="NTF25" s="21"/>
+      <c r="NTJ25" s="21"/>
+      <c r="NTN25" s="21"/>
+      <c r="NTR25" s="21"/>
+      <c r="NTV25" s="21"/>
+      <c r="NTZ25" s="21"/>
+      <c r="NUD25" s="21"/>
+      <c r="NUH25" s="21"/>
+      <c r="NUL25" s="21"/>
+      <c r="NUP25" s="21"/>
+      <c r="NUT25" s="21"/>
+      <c r="NUX25" s="21"/>
+      <c r="NVB25" s="21"/>
+      <c r="NVF25" s="21"/>
+      <c r="NVJ25" s="21"/>
+      <c r="NVN25" s="21"/>
+      <c r="NVR25" s="21"/>
+      <c r="NVV25" s="21"/>
+      <c r="NVZ25" s="21"/>
+      <c r="NWD25" s="21"/>
+      <c r="NWH25" s="21"/>
+      <c r="NWL25" s="21"/>
+      <c r="NWP25" s="21"/>
+      <c r="NWT25" s="21"/>
+      <c r="NWX25" s="21"/>
+      <c r="NXB25" s="21"/>
+      <c r="NXF25" s="21"/>
+      <c r="NXJ25" s="21"/>
+      <c r="NXN25" s="21"/>
+      <c r="NXR25" s="21"/>
+      <c r="NXV25" s="21"/>
+      <c r="NXZ25" s="21"/>
+      <c r="NYD25" s="21"/>
+      <c r="NYH25" s="21"/>
+      <c r="NYL25" s="21"/>
+      <c r="NYP25" s="21"/>
+      <c r="NYT25" s="21"/>
+      <c r="NYX25" s="21"/>
+      <c r="NZB25" s="21"/>
+      <c r="NZF25" s="21"/>
+      <c r="NZJ25" s="21"/>
+      <c r="NZN25" s="21"/>
+      <c r="NZR25" s="21"/>
+      <c r="NZV25" s="21"/>
+      <c r="NZZ25" s="21"/>
+      <c r="OAD25" s="21"/>
+      <c r="OAH25" s="21"/>
+      <c r="OAL25" s="21"/>
+      <c r="OAP25" s="21"/>
+      <c r="OAT25" s="21"/>
+      <c r="OAX25" s="21"/>
+      <c r="OBB25" s="21"/>
+      <c r="OBF25" s="21"/>
+      <c r="OBJ25" s="21"/>
+      <c r="OBN25" s="21"/>
+      <c r="OBR25" s="21"/>
+      <c r="OBV25" s="21"/>
+      <c r="OBZ25" s="21"/>
+      <c r="OCD25" s="21"/>
+      <c r="OCH25" s="21"/>
+      <c r="OCL25" s="21"/>
+      <c r="OCP25" s="21"/>
+      <c r="OCT25" s="21"/>
+      <c r="OCX25" s="21"/>
+      <c r="ODB25" s="21"/>
+      <c r="ODF25" s="21"/>
+      <c r="ODJ25" s="21"/>
+      <c r="ODN25" s="21"/>
+      <c r="ODR25" s="21"/>
+      <c r="ODV25" s="21"/>
+      <c r="ODZ25" s="21"/>
+      <c r="OED25" s="21"/>
+      <c r="OEH25" s="21"/>
+      <c r="OEL25" s="21"/>
+      <c r="OEP25" s="21"/>
+      <c r="OET25" s="21"/>
+      <c r="OEX25" s="21"/>
+      <c r="OFB25" s="21"/>
+      <c r="OFF25" s="21"/>
+      <c r="OFJ25" s="21"/>
+      <c r="OFN25" s="21"/>
+      <c r="OFR25" s="21"/>
+      <c r="OFV25" s="21"/>
+      <c r="OFZ25" s="21"/>
+      <c r="OGD25" s="21"/>
+      <c r="OGH25" s="21"/>
+      <c r="OGL25" s="21"/>
+      <c r="OGP25" s="21"/>
+      <c r="OGT25" s="21"/>
+      <c r="OGX25" s="21"/>
+      <c r="OHB25" s="21"/>
+      <c r="OHF25" s="21"/>
+      <c r="OHJ25" s="21"/>
+      <c r="OHN25" s="21"/>
+      <c r="OHR25" s="21"/>
+      <c r="OHV25" s="21"/>
+      <c r="OHZ25" s="21"/>
+      <c r="OID25" s="21"/>
+      <c r="OIH25" s="21"/>
+      <c r="OIL25" s="21"/>
+      <c r="OIP25" s="21"/>
+      <c r="OIT25" s="21"/>
+      <c r="OIX25" s="21"/>
+      <c r="OJB25" s="21"/>
+      <c r="OJF25" s="21"/>
+      <c r="OJJ25" s="21"/>
+      <c r="OJN25" s="21"/>
+      <c r="OJR25" s="21"/>
+      <c r="OJV25" s="21"/>
+      <c r="OJZ25" s="21"/>
+      <c r="OKD25" s="21"/>
+      <c r="OKH25" s="21"/>
+      <c r="OKL25" s="21"/>
+      <c r="OKP25" s="21"/>
+      <c r="OKT25" s="21"/>
+      <c r="OKX25" s="21"/>
+      <c r="OLB25" s="21"/>
+      <c r="OLF25" s="21"/>
+      <c r="OLJ25" s="21"/>
+      <c r="OLN25" s="21"/>
+      <c r="OLR25" s="21"/>
+      <c r="OLV25" s="21"/>
+      <c r="OLZ25" s="21"/>
+      <c r="OMD25" s="21"/>
+      <c r="OMH25" s="21"/>
+      <c r="OML25" s="21"/>
+      <c r="OMP25" s="21"/>
+      <c r="OMT25" s="21"/>
+      <c r="OMX25" s="21"/>
+      <c r="ONB25" s="21"/>
+      <c r="ONF25" s="21"/>
+      <c r="ONJ25" s="21"/>
+      <c r="ONN25" s="21"/>
+      <c r="ONR25" s="21"/>
+      <c r="ONV25" s="21"/>
+      <c r="ONZ25" s="21"/>
+      <c r="OOD25" s="21"/>
+      <c r="OOH25" s="21"/>
+      <c r="OOL25" s="21"/>
+      <c r="OOP25" s="21"/>
+      <c r="OOT25" s="21"/>
+      <c r="OOX25" s="21"/>
+      <c r="OPB25" s="21"/>
+      <c r="OPF25" s="21"/>
+      <c r="OPJ25" s="21"/>
+      <c r="OPN25" s="21"/>
+      <c r="OPR25" s="21"/>
+      <c r="OPV25" s="21"/>
+      <c r="OPZ25" s="21"/>
+      <c r="OQD25" s="21"/>
+      <c r="OQH25" s="21"/>
+      <c r="OQL25" s="21"/>
+      <c r="OQP25" s="21"/>
+      <c r="OQT25" s="21"/>
+      <c r="OQX25" s="21"/>
+      <c r="ORB25" s="21"/>
+      <c r="ORF25" s="21"/>
+      <c r="ORJ25" s="21"/>
+      <c r="ORN25" s="21"/>
+      <c r="ORR25" s="21"/>
+      <c r="ORV25" s="21"/>
+      <c r="ORZ25" s="21"/>
+      <c r="OSD25" s="21"/>
+      <c r="OSH25" s="21"/>
+      <c r="OSL25" s="21"/>
+      <c r="OSP25" s="21"/>
+      <c r="OST25" s="21"/>
+      <c r="OSX25" s="21"/>
+      <c r="OTB25" s="21"/>
+      <c r="OTF25" s="21"/>
+      <c r="OTJ25" s="21"/>
+      <c r="OTN25" s="21"/>
+      <c r="OTR25" s="21"/>
+      <c r="OTV25" s="21"/>
+      <c r="OTZ25" s="21"/>
+      <c r="OUD25" s="21"/>
+      <c r="OUH25" s="21"/>
+      <c r="OUL25" s="21"/>
+      <c r="OUP25" s="21"/>
+      <c r="OUT25" s="21"/>
+      <c r="OUX25" s="21"/>
+      <c r="OVB25" s="21"/>
+      <c r="OVF25" s="21"/>
+      <c r="OVJ25" s="21"/>
+      <c r="OVN25" s="21"/>
+      <c r="OVR25" s="21"/>
+      <c r="OVV25" s="21"/>
+      <c r="OVZ25" s="21"/>
+      <c r="OWD25" s="21"/>
+      <c r="OWH25" s="21"/>
+      <c r="OWL25" s="21"/>
+      <c r="OWP25" s="21"/>
+      <c r="OWT25" s="21"/>
+      <c r="OWX25" s="21"/>
+      <c r="OXB25" s="21"/>
+      <c r="OXF25" s="21"/>
+      <c r="OXJ25" s="21"/>
+      <c r="OXN25" s="21"/>
+      <c r="OXR25" s="21"/>
+      <c r="OXV25" s="21"/>
+      <c r="OXZ25" s="21"/>
+      <c r="OYD25" s="21"/>
+      <c r="OYH25" s="21"/>
+      <c r="OYL25" s="21"/>
+      <c r="OYP25" s="21"/>
+      <c r="OYT25" s="21"/>
+      <c r="OYX25" s="21"/>
+      <c r="OZB25" s="21"/>
+      <c r="OZF25" s="21"/>
+      <c r="OZJ25" s="21"/>
+      <c r="OZN25" s="21"/>
+      <c r="OZR25" s="21"/>
+      <c r="OZV25" s="21"/>
+      <c r="OZZ25" s="21"/>
+      <c r="PAD25" s="21"/>
+      <c r="PAH25" s="21"/>
+      <c r="PAL25" s="21"/>
+      <c r="PAP25" s="21"/>
+      <c r="PAT25" s="21"/>
+      <c r="PAX25" s="21"/>
+      <c r="PBB25" s="21"/>
+      <c r="PBF25" s="21"/>
+      <c r="PBJ25" s="21"/>
+      <c r="PBN25" s="21"/>
+      <c r="PBR25" s="21"/>
+      <c r="PBV25" s="21"/>
+      <c r="PBZ25" s="21"/>
+      <c r="PCD25" s="21"/>
+      <c r="PCH25" s="21"/>
+      <c r="PCL25" s="21"/>
+      <c r="PCP25" s="21"/>
+      <c r="PCT25" s="21"/>
+      <c r="PCX25" s="21"/>
+      <c r="PDB25" s="21"/>
+      <c r="PDF25" s="21"/>
+      <c r="PDJ25" s="21"/>
+      <c r="PDN25" s="21"/>
+      <c r="PDR25" s="21"/>
+      <c r="PDV25" s="21"/>
+      <c r="PDZ25" s="21"/>
+      <c r="PED25" s="21"/>
+      <c r="PEH25" s="21"/>
+      <c r="PEL25" s="21"/>
+      <c r="PEP25" s="21"/>
+      <c r="PET25" s="21"/>
+      <c r="PEX25" s="21"/>
+      <c r="PFB25" s="21"/>
+      <c r="PFF25" s="21"/>
+      <c r="PFJ25" s="21"/>
+      <c r="PFN25" s="21"/>
+      <c r="PFR25" s="21"/>
+      <c r="PFV25" s="21"/>
+      <c r="PFZ25" s="21"/>
+      <c r="PGD25" s="21"/>
+      <c r="PGH25" s="21"/>
+      <c r="PGL25" s="21"/>
+      <c r="PGP25" s="21"/>
+      <c r="PGT25" s="21"/>
+      <c r="PGX25" s="21"/>
+      <c r="PHB25" s="21"/>
+      <c r="PHF25" s="21"/>
+      <c r="PHJ25" s="21"/>
+      <c r="PHN25" s="21"/>
+      <c r="PHR25" s="21"/>
+      <c r="PHV25" s="21"/>
+      <c r="PHZ25" s="21"/>
+      <c r="PID25" s="21"/>
+      <c r="PIH25" s="21"/>
+      <c r="PIL25" s="21"/>
+      <c r="PIP25" s="21"/>
+      <c r="PIT25" s="21"/>
+      <c r="PIX25" s="21"/>
+      <c r="PJB25" s="21"/>
+      <c r="PJF25" s="21"/>
+      <c r="PJJ25" s="21"/>
+      <c r="PJN25" s="21"/>
+      <c r="PJR25" s="21"/>
+      <c r="PJV25" s="21"/>
+      <c r="PJZ25" s="21"/>
+      <c r="PKD25" s="21"/>
+      <c r="PKH25" s="21"/>
+      <c r="PKL25" s="21"/>
+      <c r="PKP25" s="21"/>
+      <c r="PKT25" s="21"/>
+      <c r="PKX25" s="21"/>
+      <c r="PLB25" s="21"/>
+      <c r="PLF25" s="21"/>
+      <c r="PLJ25" s="21"/>
+      <c r="PLN25" s="21"/>
+      <c r="PLR25" s="21"/>
+      <c r="PLV25" s="21"/>
+      <c r="PLZ25" s="21"/>
+      <c r="PMD25" s="21"/>
+      <c r="PMH25" s="21"/>
+      <c r="PML25" s="21"/>
+      <c r="PMP25" s="21"/>
+      <c r="PMT25" s="21"/>
+      <c r="PMX25" s="21"/>
+      <c r="PNB25" s="21"/>
+      <c r="PNF25" s="21"/>
+      <c r="PNJ25" s="21"/>
+      <c r="PNN25" s="21"/>
+      <c r="PNR25" s="21"/>
+      <c r="PNV25" s="21"/>
+      <c r="PNZ25" s="21"/>
+      <c r="POD25" s="21"/>
+      <c r="POH25" s="21"/>
+      <c r="POL25" s="21"/>
+      <c r="POP25" s="21"/>
+      <c r="POT25" s="21"/>
+      <c r="POX25" s="21"/>
+      <c r="PPB25" s="21"/>
+      <c r="PPF25" s="21"/>
+      <c r="PPJ25" s="21"/>
+      <c r="PPN25" s="21"/>
+      <c r="PPR25" s="21"/>
+      <c r="PPV25" s="21"/>
+      <c r="PPZ25" s="21"/>
+      <c r="PQD25" s="21"/>
+      <c r="PQH25" s="21"/>
+      <c r="PQL25" s="21"/>
+      <c r="PQP25" s="21"/>
+      <c r="PQT25" s="21"/>
+      <c r="PQX25" s="21"/>
+      <c r="PRB25" s="21"/>
+      <c r="PRF25" s="21"/>
+      <c r="PRJ25" s="21"/>
+      <c r="PRN25" s="21"/>
+      <c r="PRR25" s="21"/>
+      <c r="PRV25" s="21"/>
+      <c r="PRZ25" s="21"/>
+      <c r="PSD25" s="21"/>
+      <c r="PSH25" s="21"/>
+      <c r="PSL25" s="21"/>
+      <c r="PSP25" s="21"/>
+      <c r="PST25" s="21"/>
+      <c r="PSX25" s="21"/>
+      <c r="PTB25" s="21"/>
+      <c r="PTF25" s="21"/>
+      <c r="PTJ25" s="21"/>
+      <c r="PTN25" s="21"/>
+      <c r="PTR25" s="21"/>
+      <c r="PTV25" s="21"/>
+      <c r="PTZ25" s="21"/>
+      <c r="PUD25" s="21"/>
+      <c r="PUH25" s="21"/>
+      <c r="PUL25" s="21"/>
+      <c r="PUP25" s="21"/>
+      <c r="PUT25" s="21"/>
+      <c r="PUX25" s="21"/>
+      <c r="PVB25" s="21"/>
+      <c r="PVF25" s="21"/>
+      <c r="PVJ25" s="21"/>
+      <c r="PVN25" s="21"/>
+      <c r="PVR25" s="21"/>
+      <c r="PVV25" s="21"/>
+      <c r="PVZ25" s="21"/>
+      <c r="PWD25" s="21"/>
+      <c r="PWH25" s="21"/>
+      <c r="PWL25" s="21"/>
+      <c r="PWP25" s="21"/>
+      <c r="PWT25" s="21"/>
+      <c r="PWX25" s="21"/>
+      <c r="PXB25" s="21"/>
+      <c r="PXF25" s="21"/>
+      <c r="PXJ25" s="21"/>
+      <c r="PXN25" s="21"/>
+      <c r="PXR25" s="21"/>
+      <c r="PXV25" s="21"/>
+      <c r="PXZ25" s="21"/>
+      <c r="PYD25" s="21"/>
+      <c r="PYH25" s="21"/>
+      <c r="PYL25" s="21"/>
+      <c r="PYP25" s="21"/>
+      <c r="PYT25" s="21"/>
+      <c r="PYX25" s="21"/>
+      <c r="PZB25" s="21"/>
+      <c r="PZF25" s="21"/>
+      <c r="PZJ25" s="21"/>
+      <c r="PZN25" s="21"/>
+      <c r="PZR25" s="21"/>
+      <c r="PZV25" s="21"/>
+      <c r="PZZ25" s="21"/>
+      <c r="QAD25" s="21"/>
+      <c r="QAH25" s="21"/>
+      <c r="QAL25" s="21"/>
+      <c r="QAP25" s="21"/>
+      <c r="QAT25" s="21"/>
+      <c r="QAX25" s="21"/>
+      <c r="QBB25" s="21"/>
+      <c r="QBF25" s="21"/>
+      <c r="QBJ25" s="21"/>
+      <c r="QBN25" s="21"/>
+      <c r="QBR25" s="21"/>
+      <c r="QBV25" s="21"/>
+      <c r="QBZ25" s="21"/>
+      <c r="QCD25" s="21"/>
+      <c r="QCH25" s="21"/>
+      <c r="QCL25" s="21"/>
+      <c r="QCP25" s="21"/>
+      <c r="QCT25" s="21"/>
+      <c r="QCX25" s="21"/>
+      <c r="QDB25" s="21"/>
+      <c r="QDF25" s="21"/>
+      <c r="QDJ25" s="21"/>
+      <c r="QDN25" s="21"/>
+      <c r="QDR25" s="21"/>
+      <c r="QDV25" s="21"/>
+      <c r="QDZ25" s="21"/>
+      <c r="QED25" s="21"/>
+      <c r="QEH25" s="21"/>
+      <c r="QEL25" s="21"/>
+      <c r="QEP25" s="21"/>
+      <c r="QET25" s="21"/>
+      <c r="QEX25" s="21"/>
+      <c r="QFB25" s="21"/>
+      <c r="QFF25" s="21"/>
+      <c r="QFJ25" s="21"/>
+      <c r="QFN25" s="21"/>
+      <c r="QFR25" s="21"/>
+      <c r="QFV25" s="21"/>
+      <c r="QFZ25" s="21"/>
+      <c r="QGD25" s="21"/>
+      <c r="QGH25" s="21"/>
+      <c r="QGL25" s="21"/>
+      <c r="QGP25" s="21"/>
+      <c r="QGT25" s="21"/>
+      <c r="QGX25" s="21"/>
+      <c r="QHB25" s="21"/>
+      <c r="QHF25" s="21"/>
+      <c r="QHJ25" s="21"/>
+      <c r="QHN25" s="21"/>
+      <c r="QHR25" s="21"/>
+      <c r="QHV25" s="21"/>
+      <c r="QHZ25" s="21"/>
+      <c r="QID25" s="21"/>
+      <c r="QIH25" s="21"/>
+      <c r="QIL25" s="21"/>
+      <c r="QIP25" s="21"/>
+      <c r="QIT25" s="21"/>
+      <c r="QIX25" s="21"/>
+      <c r="QJB25" s="21"/>
+      <c r="QJF25" s="21"/>
+      <c r="QJJ25" s="21"/>
+      <c r="QJN25" s="21"/>
+      <c r="QJR25" s="21"/>
+      <c r="QJV25" s="21"/>
+      <c r="QJZ25" s="21"/>
+      <c r="QKD25" s="21"/>
+      <c r="QKH25" s="21"/>
+      <c r="QKL25" s="21"/>
+      <c r="QKP25" s="21"/>
+      <c r="QKT25" s="21"/>
+      <c r="QKX25" s="21"/>
+      <c r="QLB25" s="21"/>
+      <c r="QLF25" s="21"/>
+      <c r="QLJ25" s="21"/>
+      <c r="QLN25" s="21"/>
+      <c r="QLR25" s="21"/>
+      <c r="QLV25" s="21"/>
+      <c r="QLZ25" s="21"/>
+      <c r="QMD25" s="21"/>
+      <c r="QMH25" s="21"/>
+      <c r="QML25" s="21"/>
+      <c r="QMP25" s="21"/>
+      <c r="QMT25" s="21"/>
+      <c r="QMX25" s="21"/>
+      <c r="QNB25" s="21"/>
+      <c r="QNF25" s="21"/>
+      <c r="QNJ25" s="21"/>
+      <c r="QNN25" s="21"/>
+      <c r="QNR25" s="21"/>
+      <c r="QNV25" s="21"/>
+      <c r="QNZ25" s="21"/>
+      <c r="QOD25" s="21"/>
+      <c r="QOH25" s="21"/>
+      <c r="QOL25" s="21"/>
+      <c r="QOP25" s="21"/>
+      <c r="QOT25" s="21"/>
+      <c r="QOX25" s="21"/>
+      <c r="QPB25" s="21"/>
+      <c r="QPF25" s="21"/>
+      <c r="QPJ25" s="21"/>
+      <c r="QPN25" s="21"/>
+      <c r="QPR25" s="21"/>
+      <c r="QPV25" s="21"/>
+      <c r="QPZ25" s="21"/>
+      <c r="QQD25" s="21"/>
+      <c r="QQH25" s="21"/>
+      <c r="QQL25" s="21"/>
+      <c r="QQP25" s="21"/>
+      <c r="QQT25" s="21"/>
+      <c r="QQX25" s="21"/>
+      <c r="QRB25" s="21"/>
+      <c r="QRF25" s="21"/>
+      <c r="QRJ25" s="21"/>
+      <c r="QRN25" s="21"/>
+      <c r="QRR25" s="21"/>
+      <c r="QRV25" s="21"/>
+      <c r="QRZ25" s="21"/>
+      <c r="QSD25" s="21"/>
+      <c r="QSH25" s="21"/>
+      <c r="QSL25" s="21"/>
+      <c r="QSP25" s="21"/>
+      <c r="QST25" s="21"/>
+      <c r="QSX25" s="21"/>
+      <c r="QTB25" s="21"/>
+      <c r="QTF25" s="21"/>
+      <c r="QTJ25" s="21"/>
+      <c r="QTN25" s="21"/>
+      <c r="QTR25" s="21"/>
+      <c r="QTV25" s="21"/>
+      <c r="QTZ25" s="21"/>
+      <c r="QUD25" s="21"/>
+      <c r="QUH25" s="21"/>
+      <c r="QUL25" s="21"/>
+      <c r="QUP25" s="21"/>
+      <c r="QUT25" s="21"/>
+      <c r="QUX25" s="21"/>
+      <c r="QVB25" s="21"/>
+      <c r="QVF25" s="21"/>
+      <c r="QVJ25" s="21"/>
+      <c r="QVN25" s="21"/>
+      <c r="QVR25" s="21"/>
+      <c r="QVV25" s="21"/>
+      <c r="QVZ25" s="21"/>
+      <c r="QWD25" s="21"/>
+      <c r="QWH25" s="21"/>
+      <c r="QWL25" s="21"/>
+      <c r="QWP25" s="21"/>
+      <c r="QWT25" s="21"/>
+      <c r="QWX25" s="21"/>
+      <c r="QXB25" s="21"/>
+      <c r="QXF25" s="21"/>
+      <c r="QXJ25" s="21"/>
+      <c r="QXN25" s="21"/>
+      <c r="QXR25" s="21"/>
+      <c r="QXV25" s="21"/>
+      <c r="QXZ25" s="21"/>
+      <c r="QYD25" s="21"/>
+      <c r="QYH25" s="21"/>
+      <c r="QYL25" s="21"/>
+      <c r="QYP25" s="21"/>
+      <c r="QYT25" s="21"/>
+      <c r="QYX25" s="21"/>
+      <c r="QZB25" s="21"/>
+      <c r="QZF25" s="21"/>
+      <c r="QZJ25" s="21"/>
+      <c r="QZN25" s="21"/>
+      <c r="QZR25" s="21"/>
+      <c r="QZV25" s="21"/>
+      <c r="QZZ25" s="21"/>
+      <c r="RAD25" s="21"/>
+      <c r="RAH25" s="21"/>
+      <c r="RAL25" s="21"/>
+      <c r="RAP25" s="21"/>
+      <c r="RAT25" s="21"/>
+      <c r="RAX25" s="21"/>
+      <c r="RBB25" s="21"/>
+      <c r="RBF25" s="21"/>
+      <c r="RBJ25" s="21"/>
+      <c r="RBN25" s="21"/>
+      <c r="RBR25" s="21"/>
+      <c r="RBV25" s="21"/>
+      <c r="RBZ25" s="21"/>
+      <c r="RCD25" s="21"/>
+      <c r="RCH25" s="21"/>
+      <c r="RCL25" s="21"/>
+      <c r="RCP25" s="21"/>
+      <c r="RCT25" s="21"/>
+      <c r="RCX25" s="21"/>
+      <c r="RDB25" s="21"/>
+      <c r="RDF25" s="21"/>
+      <c r="RDJ25" s="21"/>
+      <c r="RDN25" s="21"/>
+      <c r="RDR25" s="21"/>
+      <c r="RDV25" s="21"/>
+      <c r="RDZ25" s="21"/>
+      <c r="RED25" s="21"/>
+      <c r="REH25" s="21"/>
+      <c r="REL25" s="21"/>
+      <c r="REP25" s="21"/>
+      <c r="RET25" s="21"/>
+      <c r="REX25" s="21"/>
+      <c r="RFB25" s="21"/>
+      <c r="RFF25" s="21"/>
+      <c r="RFJ25" s="21"/>
+      <c r="RFN25" s="21"/>
+      <c r="RFR25" s="21"/>
+      <c r="RFV25" s="21"/>
+      <c r="RFZ25" s="21"/>
+      <c r="RGD25" s="21"/>
+      <c r="RGH25" s="21"/>
+      <c r="RGL25" s="21"/>
+      <c r="RGP25" s="21"/>
+      <c r="RGT25" s="21"/>
+      <c r="RGX25" s="21"/>
+      <c r="RHB25" s="21"/>
+      <c r="RHF25" s="21"/>
+      <c r="RHJ25" s="21"/>
+      <c r="RHN25" s="21"/>
+      <c r="RHR25" s="21"/>
+      <c r="RHV25" s="21"/>
+      <c r="RHZ25" s="21"/>
+      <c r="RID25" s="21"/>
+      <c r="RIH25" s="21"/>
+      <c r="RIL25" s="21"/>
+      <c r="RIP25" s="21"/>
+      <c r="RIT25" s="21"/>
+      <c r="RIX25" s="21"/>
+      <c r="RJB25" s="21"/>
+      <c r="RJF25" s="21"/>
+      <c r="RJJ25" s="21"/>
+      <c r="RJN25" s="21"/>
+      <c r="RJR25" s="21"/>
+      <c r="RJV25" s="21"/>
+      <c r="RJZ25" s="21"/>
+      <c r="RKD25" s="21"/>
+      <c r="RKH25" s="21"/>
+      <c r="RKL25" s="21"/>
+      <c r="RKP25" s="21"/>
+      <c r="RKT25" s="21"/>
+      <c r="RKX25" s="21"/>
+      <c r="RLB25" s="21"/>
+      <c r="RLF25" s="21"/>
+      <c r="RLJ25" s="21"/>
+      <c r="RLN25" s="21"/>
+      <c r="RLR25" s="21"/>
+      <c r="RLV25" s="21"/>
+      <c r="RLZ25" s="21"/>
+      <c r="RMD25" s="21"/>
+      <c r="RMH25" s="21"/>
+      <c r="RML25" s="21"/>
+      <c r="RMP25" s="21"/>
+      <c r="RMT25" s="21"/>
+      <c r="RMX25" s="21"/>
+      <c r="RNB25" s="21"/>
+      <c r="RNF25" s="21"/>
+      <c r="RNJ25" s="21"/>
+      <c r="RNN25" s="21"/>
+      <c r="RNR25" s="21"/>
+      <c r="RNV25" s="21"/>
+      <c r="RNZ25" s="21"/>
+      <c r="ROD25" s="21"/>
+      <c r="ROH25" s="21"/>
+      <c r="ROL25" s="21"/>
+      <c r="ROP25" s="21"/>
+      <c r="ROT25" s="21"/>
+      <c r="ROX25" s="21"/>
+      <c r="RPB25" s="21"/>
+      <c r="RPF25" s="21"/>
+      <c r="RPJ25" s="21"/>
+      <c r="RPN25" s="21"/>
+      <c r="RPR25" s="21"/>
+      <c r="RPV25" s="21"/>
+      <c r="RPZ25" s="21"/>
+      <c r="RQD25" s="21"/>
+      <c r="RQH25" s="21"/>
+      <c r="RQL25" s="21"/>
+      <c r="RQP25" s="21"/>
+      <c r="RQT25" s="21"/>
+      <c r="RQX25" s="21"/>
+      <c r="RRB25" s="21"/>
+      <c r="RRF25" s="21"/>
+      <c r="RRJ25" s="21"/>
+      <c r="RRN25" s="21"/>
+      <c r="RRR25" s="21"/>
+      <c r="RRV25" s="21"/>
+      <c r="RRZ25" s="21"/>
+      <c r="RSD25" s="21"/>
+      <c r="RSH25" s="21"/>
+      <c r="RSL25" s="21"/>
+      <c r="RSP25" s="21"/>
+      <c r="RST25" s="21"/>
+      <c r="RSX25" s="21"/>
+      <c r="RTB25" s="21"/>
+      <c r="RTF25" s="21"/>
+      <c r="RTJ25" s="21"/>
+      <c r="RTN25" s="21"/>
+      <c r="RTR25" s="21"/>
+      <c r="RTV25" s="21"/>
+      <c r="RTZ25" s="21"/>
+      <c r="RUD25" s="21"/>
+      <c r="RUH25" s="21"/>
+      <c r="RUL25" s="21"/>
+      <c r="RUP25" s="21"/>
+      <c r="RUT25" s="21"/>
+      <c r="RUX25" s="21"/>
+      <c r="RVB25" s="21"/>
+      <c r="RVF25" s="21"/>
+      <c r="RVJ25" s="21"/>
+      <c r="RVN25" s="21"/>
+      <c r="RVR25" s="21"/>
+      <c r="RVV25" s="21"/>
+      <c r="RVZ25" s="21"/>
+      <c r="RWD25" s="21"/>
+      <c r="RWH25" s="21"/>
+      <c r="RWL25" s="21"/>
+      <c r="RWP25" s="21"/>
+      <c r="RWT25" s="21"/>
+      <c r="RWX25" s="21"/>
+      <c r="RXB25" s="21"/>
+      <c r="RXF25" s="21"/>
+      <c r="RXJ25" s="21"/>
+      <c r="RXN25" s="21"/>
+      <c r="RXR25" s="21"/>
+      <c r="RXV25" s="21"/>
+      <c r="RXZ25" s="21"/>
+      <c r="RYD25" s="21"/>
+      <c r="RYH25" s="21"/>
+      <c r="RYL25" s="21"/>
+      <c r="RYP25" s="21"/>
+      <c r="RYT25" s="21"/>
+      <c r="RYX25" s="21"/>
+      <c r="RZB25" s="21"/>
+      <c r="RZF25" s="21"/>
+      <c r="RZJ25" s="21"/>
+      <c r="RZN25" s="21"/>
+      <c r="RZR25" s="21"/>
+      <c r="RZV25" s="21"/>
+      <c r="RZZ25" s="21"/>
+      <c r="SAD25" s="21"/>
+      <c r="SAH25" s="21"/>
+      <c r="SAL25" s="21"/>
+      <c r="SAP25" s="21"/>
+      <c r="SAT25" s="21"/>
+      <c r="SAX25" s="21"/>
+      <c r="SBB25" s="21"/>
+      <c r="SBF25" s="21"/>
+      <c r="SBJ25" s="21"/>
+      <c r="SBN25" s="21"/>
+      <c r="SBR25" s="21"/>
+      <c r="SBV25" s="21"/>
+      <c r="SBZ25" s="21"/>
+      <c r="SCD25" s="21"/>
+      <c r="SCH25" s="21"/>
+      <c r="SCL25" s="21"/>
+      <c r="SCP25" s="21"/>
+      <c r="SCT25" s="21"/>
+      <c r="SCX25" s="21"/>
+      <c r="SDB25" s="21"/>
+      <c r="SDF25" s="21"/>
+      <c r="SDJ25" s="21"/>
+      <c r="SDN25" s="21"/>
+      <c r="SDR25" s="21"/>
+      <c r="SDV25" s="21"/>
+      <c r="SDZ25" s="21"/>
+      <c r="SED25" s="21"/>
+      <c r="SEH25" s="21"/>
+      <c r="SEL25" s="21"/>
+      <c r="SEP25" s="21"/>
+      <c r="SET25" s="21"/>
+      <c r="SEX25" s="21"/>
+      <c r="SFB25" s="21"/>
+      <c r="SFF25" s="21"/>
+      <c r="SFJ25" s="21"/>
+      <c r="SFN25" s="21"/>
+      <c r="SFR25" s="21"/>
+      <c r="SFV25" s="21"/>
+      <c r="SFZ25" s="21"/>
+      <c r="SGD25" s="21"/>
+      <c r="SGH25" s="21"/>
+      <c r="SGL25" s="21"/>
+      <c r="SGP25" s="21"/>
+      <c r="SGT25" s="21"/>
+      <c r="SGX25" s="21"/>
+      <c r="SHB25" s="21"/>
+      <c r="SHF25" s="21"/>
+      <c r="SHJ25" s="21"/>
+      <c r="SHN25" s="21"/>
+      <c r="SHR25" s="21"/>
+      <c r="SHV25" s="21"/>
+      <c r="SHZ25" s="21"/>
+      <c r="SID25" s="21"/>
+      <c r="SIH25" s="21"/>
+      <c r="SIL25" s="21"/>
+      <c r="SIP25" s="21"/>
+      <c r="SIT25" s="21"/>
+      <c r="SIX25" s="21"/>
+      <c r="SJB25" s="21"/>
+      <c r="SJF25" s="21"/>
+      <c r="SJJ25" s="21"/>
+      <c r="SJN25" s="21"/>
+      <c r="SJR25" s="21"/>
+      <c r="SJV25" s="21"/>
+      <c r="SJZ25" s="21"/>
+      <c r="SKD25" s="21"/>
+      <c r="SKH25" s="21"/>
+      <c r="SKL25" s="21"/>
+      <c r="SKP25" s="21"/>
+      <c r="SKT25" s="21"/>
+      <c r="SKX25" s="21"/>
+      <c r="SLB25" s="21"/>
+      <c r="SLF25" s="21"/>
+      <c r="SLJ25" s="21"/>
+      <c r="SLN25" s="21"/>
+      <c r="SLR25" s="21"/>
+      <c r="SLV25" s="21"/>
+      <c r="SLZ25" s="21"/>
+      <c r="SMD25" s="21"/>
+      <c r="SMH25" s="21"/>
+      <c r="SML25" s="21"/>
+      <c r="SMP25" s="21"/>
+      <c r="SMT25" s="21"/>
+      <c r="SMX25" s="21"/>
+      <c r="SNB25" s="21"/>
+      <c r="SNF25" s="21"/>
+      <c r="SNJ25" s="21"/>
+      <c r="SNN25" s="21"/>
+      <c r="SNR25" s="21"/>
+      <c r="SNV25" s="21"/>
+      <c r="SNZ25" s="21"/>
+      <c r="SOD25" s="21"/>
+      <c r="SOH25" s="21"/>
+      <c r="SOL25" s="21"/>
+      <c r="SOP25" s="21"/>
+      <c r="SOT25" s="21"/>
+      <c r="SOX25" s="21"/>
+      <c r="SPB25" s="21"/>
+      <c r="SPF25" s="21"/>
+      <c r="SPJ25" s="21"/>
+      <c r="SPN25" s="21"/>
+      <c r="SPR25" s="21"/>
+      <c r="SPV25" s="21"/>
+      <c r="SPZ25" s="21"/>
+      <c r="SQD25" s="21"/>
+      <c r="SQH25" s="21"/>
+      <c r="SQL25" s="21"/>
+      <c r="SQP25" s="21"/>
+      <c r="SQT25" s="21"/>
+      <c r="SQX25" s="21"/>
+      <c r="SRB25" s="21"/>
+      <c r="SRF25" s="21"/>
+      <c r="SRJ25" s="21"/>
+      <c r="SRN25" s="21"/>
+      <c r="SRR25" s="21"/>
+      <c r="SRV25" s="21"/>
+      <c r="SRZ25" s="21"/>
+      <c r="SSD25" s="21"/>
+      <c r="SSH25" s="21"/>
+      <c r="SSL25" s="21"/>
+      <c r="SSP25" s="21"/>
+      <c r="SST25" s="21"/>
+      <c r="SSX25" s="21"/>
+      <c r="STB25" s="21"/>
+      <c r="STF25" s="21"/>
+      <c r="STJ25" s="21"/>
+      <c r="STN25" s="21"/>
+      <c r="STR25" s="21"/>
+      <c r="STV25" s="21"/>
+      <c r="STZ25" s="21"/>
+      <c r="SUD25" s="21"/>
+      <c r="SUH25" s="21"/>
+      <c r="SUL25" s="21"/>
+      <c r="SUP25" s="21"/>
+      <c r="SUT25" s="21"/>
+      <c r="SUX25" s="21"/>
+      <c r="SVB25" s="21"/>
+      <c r="SVF25" s="21"/>
+      <c r="SVJ25" s="21"/>
+      <c r="SVN25" s="21"/>
+      <c r="SVR25" s="21"/>
+      <c r="SVV25" s="21"/>
+      <c r="SVZ25" s="21"/>
+      <c r="SWD25" s="21"/>
+      <c r="SWH25" s="21"/>
+      <c r="SWL25" s="21"/>
+      <c r="SWP25" s="21"/>
+      <c r="SWT25" s="21"/>
+      <c r="SWX25" s="21"/>
+      <c r="SXB25" s="21"/>
+      <c r="SXF25" s="21"/>
+      <c r="SXJ25" s="21"/>
+      <c r="SXN25" s="21"/>
+      <c r="SXR25" s="21"/>
+      <c r="SXV25" s="21"/>
+      <c r="SXZ25" s="21"/>
+      <c r="SYD25" s="21"/>
+      <c r="SYH25" s="21"/>
+      <c r="SYL25" s="21"/>
+      <c r="SYP25" s="21"/>
+      <c r="SYT25" s="21"/>
+      <c r="SYX25" s="21"/>
+      <c r="SZB25" s="21"/>
+      <c r="SZF25" s="21"/>
+      <c r="SZJ25" s="21"/>
+      <c r="SZN25" s="21"/>
+      <c r="SZR25" s="21"/>
+      <c r="SZV25" s="21"/>
+      <c r="SZZ25" s="21"/>
+      <c r="TAD25" s="21"/>
+      <c r="TAH25" s="21"/>
+      <c r="TAL25" s="21"/>
+      <c r="TAP25" s="21"/>
+      <c r="TAT25" s="21"/>
+      <c r="TAX25" s="21"/>
+      <c r="TBB25" s="21"/>
+      <c r="TBF25" s="21"/>
+      <c r="TBJ25" s="21"/>
+      <c r="TBN25" s="21"/>
+      <c r="TBR25" s="21"/>
+      <c r="TBV25" s="21"/>
+      <c r="TBZ25" s="21"/>
+      <c r="TCD25" s="21"/>
+      <c r="TCH25" s="21"/>
+      <c r="TCL25" s="21"/>
+      <c r="TCP25" s="21"/>
+      <c r="TCT25" s="21"/>
+      <c r="TCX25" s="21"/>
+      <c r="TDB25" s="21"/>
+      <c r="TDF25" s="21"/>
+      <c r="TDJ25" s="21"/>
+      <c r="TDN25" s="21"/>
+      <c r="TDR25" s="21"/>
+      <c r="TDV25" s="21"/>
+      <c r="TDZ25" s="21"/>
+      <c r="TED25" s="21"/>
+      <c r="TEH25" s="21"/>
+      <c r="TEL25" s="21"/>
+      <c r="TEP25" s="21"/>
+      <c r="TET25" s="21"/>
+      <c r="TEX25" s="21"/>
+      <c r="TFB25" s="21"/>
+      <c r="TFF25" s="21"/>
+      <c r="TFJ25" s="21"/>
+      <c r="TFN25" s="21"/>
+      <c r="TFR25" s="21"/>
+      <c r="TFV25" s="21"/>
+      <c r="TFZ25" s="21"/>
+      <c r="TGD25" s="21"/>
+      <c r="TGH25" s="21"/>
+      <c r="TGL25" s="21"/>
+      <c r="TGP25" s="21"/>
+      <c r="TGT25" s="21"/>
+      <c r="TGX25" s="21"/>
+      <c r="THB25" s="21"/>
+      <c r="THF25" s="21"/>
+      <c r="THJ25" s="21"/>
+      <c r="THN25" s="21"/>
+      <c r="THR25" s="21"/>
+      <c r="THV25" s="21"/>
+      <c r="THZ25" s="21"/>
+      <c r="TID25" s="21"/>
+      <c r="TIH25" s="21"/>
+      <c r="TIL25" s="21"/>
+      <c r="TIP25" s="21"/>
+      <c r="TIT25" s="21"/>
+      <c r="TIX25" s="21"/>
+      <c r="TJB25" s="21"/>
+      <c r="TJF25" s="21"/>
+      <c r="TJJ25" s="21"/>
+      <c r="TJN25" s="21"/>
+      <c r="TJR25" s="21"/>
+      <c r="TJV25" s="21"/>
+      <c r="TJZ25" s="21"/>
+      <c r="TKD25" s="21"/>
+      <c r="TKH25" s="21"/>
+      <c r="TKL25" s="21"/>
+      <c r="TKP25" s="21"/>
+      <c r="TKT25" s="21"/>
+      <c r="TKX25" s="21"/>
+      <c r="TLB25" s="21"/>
+      <c r="TLF25" s="21"/>
+      <c r="TLJ25" s="21"/>
+      <c r="TLN25" s="21"/>
+      <c r="TLR25" s="21"/>
+      <c r="TLV25" s="21"/>
+      <c r="TLZ25" s="21"/>
+      <c r="TMD25" s="21"/>
+      <c r="TMH25" s="21"/>
+      <c r="TML25" s="21"/>
+      <c r="TMP25" s="21"/>
+      <c r="TMT25" s="21"/>
+      <c r="TMX25" s="21"/>
+      <c r="TNB25" s="21"/>
+      <c r="TNF25" s="21"/>
+      <c r="TNJ25" s="21"/>
+      <c r="TNN25" s="21"/>
+      <c r="TNR25" s="21"/>
+      <c r="TNV25" s="21"/>
+      <c r="TNZ25" s="21"/>
+      <c r="TOD25" s="21"/>
+      <c r="TOH25" s="21"/>
+      <c r="TOL25" s="21"/>
+      <c r="TOP25" s="21"/>
+      <c r="TOT25" s="21"/>
+      <c r="TOX25" s="21"/>
+      <c r="TPB25" s="21"/>
+      <c r="TPF25" s="21"/>
+      <c r="TPJ25" s="21"/>
+      <c r="TPN25" s="21"/>
+      <c r="TPR25" s="21"/>
+      <c r="TPV25" s="21"/>
+      <c r="TPZ25" s="21"/>
+      <c r="TQD25" s="21"/>
+      <c r="TQH25" s="21"/>
+      <c r="TQL25" s="21"/>
+      <c r="TQP25" s="21"/>
+      <c r="TQT25" s="21"/>
+      <c r="TQX25" s="21"/>
+      <c r="TRB25" s="21"/>
+      <c r="TRF25" s="21"/>
+      <c r="TRJ25" s="21"/>
+      <c r="TRN25" s="21"/>
+      <c r="TRR25" s="21"/>
+      <c r="TRV25" s="21"/>
+      <c r="TRZ25" s="21"/>
+      <c r="TSD25" s="21"/>
+      <c r="TSH25" s="21"/>
+      <c r="TSL25" s="21"/>
+      <c r="TSP25" s="21"/>
+      <c r="TST25" s="21"/>
+      <c r="TSX25" s="21"/>
+      <c r="TTB25" s="21"/>
+      <c r="TTF25" s="21"/>
+      <c r="TTJ25" s="21"/>
+      <c r="TTN25" s="21"/>
+      <c r="TTR25" s="21"/>
+      <c r="TTV25" s="21"/>
+      <c r="TTZ25" s="21"/>
+      <c r="TUD25" s="21"/>
+      <c r="TUH25" s="21"/>
+      <c r="TUL25" s="21"/>
+      <c r="TUP25" s="21"/>
+      <c r="TUT25" s="21"/>
+      <c r="TUX25" s="21"/>
+      <c r="TVB25" s="21"/>
+      <c r="TVF25" s="21"/>
+      <c r="TVJ25" s="21"/>
+      <c r="TVN25" s="21"/>
+      <c r="TVR25" s="21"/>
+      <c r="TVV25" s="21"/>
+      <c r="TVZ25" s="21"/>
+      <c r="TWD25" s="21"/>
+      <c r="TWH25" s="21"/>
+      <c r="TWL25" s="21"/>
+      <c r="TWP25" s="21"/>
+      <c r="TWT25" s="21"/>
+      <c r="TWX25" s="21"/>
+      <c r="TXB25" s="21"/>
+      <c r="TXF25" s="21"/>
+      <c r="TXJ25" s="21"/>
+      <c r="TXN25" s="21"/>
+      <c r="TXR25" s="21"/>
+      <c r="TXV25" s="21"/>
+      <c r="TXZ25" s="21"/>
+      <c r="TYD25" s="21"/>
+      <c r="TYH25" s="21"/>
+      <c r="TYL25" s="21"/>
+      <c r="TYP25" s="21"/>
+      <c r="TYT25" s="21"/>
+      <c r="TYX25" s="21"/>
+      <c r="TZB25" s="21"/>
+      <c r="TZF25" s="21"/>
+      <c r="TZJ25" s="21"/>
+      <c r="TZN25" s="21"/>
+      <c r="TZR25" s="21"/>
+      <c r="TZV25" s="21"/>
+      <c r="TZZ25" s="21"/>
+      <c r="UAD25" s="21"/>
+      <c r="UAH25" s="21"/>
+      <c r="UAL25" s="21"/>
+      <c r="UAP25" s="21"/>
+      <c r="UAT25" s="21"/>
+      <c r="UAX25" s="21"/>
+      <c r="UBB25" s="21"/>
+      <c r="UBF25" s="21"/>
+      <c r="UBJ25" s="21"/>
+      <c r="UBN25" s="21"/>
+      <c r="UBR25" s="21"/>
+      <c r="UBV25" s="21"/>
+      <c r="UBZ25" s="21"/>
+      <c r="UCD25" s="21"/>
+      <c r="UCH25" s="21"/>
+      <c r="UCL25" s="21"/>
+      <c r="UCP25" s="21"/>
+      <c r="UCT25" s="21"/>
+      <c r="UCX25" s="21"/>
+      <c r="UDB25" s="21"/>
+      <c r="UDF25" s="21"/>
+      <c r="UDJ25" s="21"/>
+      <c r="UDN25" s="21"/>
+      <c r="UDR25" s="21"/>
+      <c r="UDV25" s="21"/>
+      <c r="UDZ25" s="21"/>
+      <c r="UED25" s="21"/>
+      <c r="UEH25" s="21"/>
+      <c r="UEL25" s="21"/>
+      <c r="UEP25" s="21"/>
+      <c r="UET25" s="21"/>
+      <c r="UEX25" s="21"/>
+      <c r="UFB25" s="21"/>
+      <c r="UFF25" s="21"/>
+      <c r="UFJ25" s="21"/>
+      <c r="UFN25" s="21"/>
+      <c r="UFR25" s="21"/>
+      <c r="UFV25" s="21"/>
+      <c r="UFZ25" s="21"/>
+      <c r="UGD25" s="21"/>
+      <c r="UGH25" s="21"/>
+      <c r="UGL25" s="21"/>
+      <c r="UGP25" s="21"/>
+      <c r="UGT25" s="21"/>
+      <c r="UGX25" s="21"/>
+      <c r="UHB25" s="21"/>
+      <c r="UHF25" s="21"/>
+      <c r="UHJ25" s="21"/>
+      <c r="UHN25" s="21"/>
+      <c r="UHR25" s="21"/>
+      <c r="UHV25" s="21"/>
+      <c r="UHZ25" s="21"/>
+      <c r="UID25" s="21"/>
+      <c r="UIH25" s="21"/>
+      <c r="UIL25" s="21"/>
+      <c r="UIP25" s="21"/>
+      <c r="UIT25" s="21"/>
+      <c r="UIX25" s="21"/>
+      <c r="UJB25" s="21"/>
+      <c r="UJF25" s="21"/>
+      <c r="UJJ25" s="21"/>
+      <c r="UJN25" s="21"/>
+      <c r="UJR25" s="21"/>
+      <c r="UJV25" s="21"/>
+      <c r="UJZ25" s="21"/>
+      <c r="UKD25" s="21"/>
+      <c r="UKH25" s="21"/>
+      <c r="UKL25" s="21"/>
+      <c r="UKP25" s="21"/>
+      <c r="UKT25" s="21"/>
+      <c r="UKX25" s="21"/>
+      <c r="ULB25" s="21"/>
+      <c r="ULF25" s="21"/>
+      <c r="ULJ25" s="21"/>
+      <c r="ULN25" s="21"/>
+      <c r="ULR25" s="21"/>
+      <c r="ULV25" s="21"/>
+      <c r="ULZ25" s="21"/>
+      <c r="UMD25" s="21"/>
+      <c r="UMH25" s="21"/>
+      <c r="UML25" s="21"/>
+      <c r="UMP25" s="21"/>
+      <c r="UMT25" s="21"/>
+      <c r="UMX25" s="21"/>
+      <c r="UNB25" s="21"/>
+      <c r="UNF25" s="21"/>
+      <c r="UNJ25" s="21"/>
+      <c r="UNN25" s="21"/>
+      <c r="UNR25" s="21"/>
+      <c r="UNV25" s="21"/>
+      <c r="UNZ25" s="21"/>
+      <c r="UOD25" s="21"/>
+      <c r="UOH25" s="21"/>
+      <c r="UOL25" s="21"/>
+      <c r="UOP25" s="21"/>
+      <c r="UOT25" s="21"/>
+      <c r="UOX25" s="21"/>
+      <c r="UPB25" s="21"/>
+      <c r="UPF25" s="21"/>
+      <c r="UPJ25" s="21"/>
+      <c r="UPN25" s="21"/>
+      <c r="UPR25" s="21"/>
+      <c r="UPV25" s="21"/>
+      <c r="UPZ25" s="21"/>
+      <c r="UQD25" s="21"/>
+      <c r="UQH25" s="21"/>
+      <c r="UQL25" s="21"/>
+      <c r="UQP25" s="21"/>
+      <c r="UQT25" s="21"/>
+      <c r="UQX25" s="21"/>
+      <c r="URB25" s="21"/>
+      <c r="URF25" s="21"/>
+      <c r="URJ25" s="21"/>
+      <c r="URN25" s="21"/>
+      <c r="URR25" s="21"/>
+      <c r="URV25" s="21"/>
+      <c r="URZ25" s="21"/>
+      <c r="USD25" s="21"/>
+      <c r="USH25" s="21"/>
+      <c r="USL25" s="21"/>
+      <c r="USP25" s="21"/>
+      <c r="UST25" s="21"/>
+      <c r="USX25" s="21"/>
+      <c r="UTB25" s="21"/>
+      <c r="UTF25" s="21"/>
+      <c r="UTJ25" s="21"/>
+      <c r="UTN25" s="21"/>
+      <c r="UTR25" s="21"/>
+      <c r="UTV25" s="21"/>
+      <c r="UTZ25" s="21"/>
+      <c r="UUD25" s="21"/>
+      <c r="UUH25" s="21"/>
+      <c r="UUL25" s="21"/>
+      <c r="UUP25" s="21"/>
+      <c r="UUT25" s="21"/>
+      <c r="UUX25" s="21"/>
+      <c r="UVB25" s="21"/>
+      <c r="UVF25" s="21"/>
+      <c r="UVJ25" s="21"/>
+      <c r="UVN25" s="21"/>
+      <c r="UVR25" s="21"/>
+      <c r="UVV25" s="21"/>
+      <c r="UVZ25" s="21"/>
+      <c r="UWD25" s="21"/>
+      <c r="UWH25" s="21"/>
+      <c r="UWL25" s="21"/>
+      <c r="UWP25" s="21"/>
+      <c r="UWT25" s="21"/>
+      <c r="UWX25" s="21"/>
+      <c r="UXB25" s="21"/>
+      <c r="UXF25" s="21"/>
+      <c r="UXJ25" s="21"/>
+      <c r="UXN25" s="21"/>
+      <c r="UXR25" s="21"/>
+      <c r="UXV25" s="21"/>
+      <c r="UXZ25" s="21"/>
+      <c r="UYD25" s="21"/>
+      <c r="UYH25" s="21"/>
+      <c r="UYL25" s="21"/>
+      <c r="UYP25" s="21"/>
+      <c r="UYT25" s="21"/>
+      <c r="UYX25" s="21"/>
+      <c r="UZB25" s="21"/>
+      <c r="UZF25" s="21"/>
+      <c r="UZJ25" s="21"/>
+      <c r="UZN25" s="21"/>
+      <c r="UZR25" s="21"/>
+      <c r="UZV25" s="21"/>
+      <c r="UZZ25" s="21"/>
+      <c r="VAD25" s="21"/>
+      <c r="VAH25" s="21"/>
+      <c r="VAL25" s="21"/>
+      <c r="VAP25" s="21"/>
+      <c r="VAT25" s="21"/>
+      <c r="VAX25" s="21"/>
+      <c r="VBB25" s="21"/>
+      <c r="VBF25" s="21"/>
+      <c r="VBJ25" s="21"/>
+      <c r="VBN25" s="21"/>
+      <c r="VBR25" s="21"/>
+      <c r="VBV25" s="21"/>
+      <c r="VBZ25" s="21"/>
+      <c r="VCD25" s="21"/>
+      <c r="VCH25" s="21"/>
+      <c r="VCL25" s="21"/>
+      <c r="VCP25" s="21"/>
+      <c r="VCT25" s="21"/>
+      <c r="VCX25" s="21"/>
+      <c r="VDB25" s="21"/>
+      <c r="VDF25" s="21"/>
+      <c r="VDJ25" s="21"/>
+      <c r="VDN25" s="21"/>
+      <c r="VDR25" s="21"/>
+      <c r="VDV25" s="21"/>
+      <c r="VDZ25" s="21"/>
+      <c r="VED25" s="21"/>
+      <c r="VEH25" s="21"/>
+      <c r="VEL25" s="21"/>
+      <c r="VEP25" s="21"/>
+      <c r="VET25" s="21"/>
+      <c r="VEX25" s="21"/>
+      <c r="VFB25" s="21"/>
+      <c r="VFF25" s="21"/>
+      <c r="VFJ25" s="21"/>
+      <c r="VFN25" s="21"/>
+      <c r="VFR25" s="21"/>
+      <c r="VFV25" s="21"/>
+      <c r="VFZ25" s="21"/>
+      <c r="VGD25" s="21"/>
+      <c r="VGH25" s="21"/>
+      <c r="VGL25" s="21"/>
+      <c r="VGP25" s="21"/>
+      <c r="VGT25" s="21"/>
+      <c r="VGX25" s="21"/>
+      <c r="VHB25" s="21"/>
+      <c r="VHF25" s="21"/>
+      <c r="VHJ25" s="21"/>
+      <c r="VHN25" s="21"/>
+      <c r="VHR25" s="21"/>
+      <c r="VHV25" s="21"/>
+      <c r="VHZ25" s="21"/>
+      <c r="VID25" s="21"/>
+      <c r="VIH25" s="21"/>
+      <c r="VIL25" s="21"/>
+      <c r="VIP25" s="21"/>
+      <c r="VIT25" s="21"/>
+      <c r="VIX25" s="21"/>
+      <c r="VJB25" s="21"/>
+      <c r="VJF25" s="21"/>
+      <c r="VJJ25" s="21"/>
+      <c r="VJN25" s="21"/>
+      <c r="VJR25" s="21"/>
+      <c r="VJV25" s="21"/>
+      <c r="VJZ25" s="21"/>
+      <c r="VKD25" s="21"/>
+      <c r="VKH25" s="21"/>
+      <c r="VKL25" s="21"/>
+      <c r="VKP25" s="21"/>
+      <c r="VKT25" s="21"/>
+      <c r="VKX25" s="21"/>
+      <c r="VLB25" s="21"/>
+      <c r="VLF25" s="21"/>
+      <c r="VLJ25" s="21"/>
+      <c r="VLN25" s="21"/>
+      <c r="VLR25" s="21"/>
+      <c r="VLV25" s="21"/>
+      <c r="VLZ25" s="21"/>
+      <c r="VMD25" s="21"/>
+      <c r="VMH25" s="21"/>
+      <c r="VML25" s="21"/>
+      <c r="VMP25" s="21"/>
+      <c r="VMT25" s="21"/>
+      <c r="VMX25" s="21"/>
+      <c r="VNB25" s="21"/>
+      <c r="VNF25" s="21"/>
+      <c r="VNJ25" s="21"/>
+      <c r="VNN25" s="21"/>
+      <c r="VNR25" s="21"/>
+      <c r="VNV25" s="21"/>
+      <c r="VNZ25" s="21"/>
+      <c r="VOD25" s="21"/>
+      <c r="VOH25" s="21"/>
+      <c r="VOL25" s="21"/>
+      <c r="VOP25" s="21"/>
+      <c r="VOT25" s="21"/>
+      <c r="VOX25" s="21"/>
+      <c r="VPB25" s="21"/>
+      <c r="VPF25" s="21"/>
+      <c r="VPJ25" s="21"/>
+      <c r="VPN25" s="21"/>
+      <c r="VPR25" s="21"/>
+      <c r="VPV25" s="21"/>
+      <c r="VPZ25" s="21"/>
+      <c r="VQD25" s="21"/>
+      <c r="VQH25" s="21"/>
+      <c r="VQL25" s="21"/>
+      <c r="VQP25" s="21"/>
+      <c r="VQT25" s="21"/>
+      <c r="VQX25" s="21"/>
+      <c r="VRB25" s="21"/>
+      <c r="VRF25" s="21"/>
+      <c r="VRJ25" s="21"/>
+      <c r="VRN25" s="21"/>
+      <c r="VRR25" s="21"/>
+      <c r="VRV25" s="21"/>
+      <c r="VRZ25" s="21"/>
+      <c r="VSD25" s="21"/>
+      <c r="VSH25" s="21"/>
+      <c r="VSL25" s="21"/>
+      <c r="VSP25" s="21"/>
+      <c r="VST25" s="21"/>
+      <c r="VSX25" s="21"/>
+      <c r="VTB25" s="21"/>
+      <c r="VTF25" s="21"/>
+      <c r="VTJ25" s="21"/>
+      <c r="VTN25" s="21"/>
+      <c r="VTR25" s="21"/>
+      <c r="VTV25" s="21"/>
+      <c r="VTZ25" s="21"/>
+      <c r="VUD25" s="21"/>
+      <c r="VUH25" s="21"/>
+      <c r="VUL25" s="21"/>
+      <c r="VUP25" s="21"/>
+      <c r="VUT25" s="21"/>
+      <c r="VUX25" s="21"/>
+      <c r="VVB25" s="21"/>
+      <c r="VVF25" s="21"/>
+      <c r="VVJ25" s="21"/>
+      <c r="VVN25" s="21"/>
+      <c r="VVR25" s="21"/>
+      <c r="VVV25" s="21"/>
+      <c r="VVZ25" s="21"/>
+      <c r="VWD25" s="21"/>
+      <c r="VWH25" s="21"/>
+      <c r="VWL25" s="21"/>
+      <c r="VWP25" s="21"/>
+      <c r="VWT25" s="21"/>
+      <c r="VWX25" s="21"/>
+      <c r="VXB25" s="21"/>
+      <c r="VXF25" s="21"/>
+      <c r="VXJ25" s="21"/>
+      <c r="VXN25" s="21"/>
+      <c r="VXR25" s="21"/>
+      <c r="VXV25" s="21"/>
+      <c r="VXZ25" s="21"/>
+      <c r="VYD25" s="21"/>
+      <c r="VYH25" s="21"/>
+      <c r="VYL25" s="21"/>
+      <c r="VYP25" s="21"/>
+      <c r="VYT25" s="21"/>
+      <c r="VYX25" s="21"/>
+      <c r="VZB25" s="21"/>
+      <c r="VZF25" s="21"/>
+      <c r="VZJ25" s="21"/>
+      <c r="VZN25" s="21"/>
+      <c r="VZR25" s="21"/>
+      <c r="VZV25" s="21"/>
+      <c r="VZZ25" s="21"/>
+      <c r="WAD25" s="21"/>
+      <c r="WAH25" s="21"/>
+      <c r="WAL25" s="21"/>
+      <c r="WAP25" s="21"/>
+      <c r="WAT25" s="21"/>
+      <c r="WAX25" s="21"/>
+      <c r="WBB25" s="21"/>
+      <c r="WBF25" s="21"/>
+      <c r="WBJ25" s="21"/>
+      <c r="WBN25" s="21"/>
+      <c r="WBR25" s="21"/>
+      <c r="WBV25" s="21"/>
+      <c r="WBZ25" s="21"/>
+      <c r="WCD25" s="21"/>
+      <c r="WCH25" s="21"/>
+      <c r="WCL25" s="21"/>
+      <c r="WCP25" s="21"/>
+      <c r="WCT25" s="21"/>
+      <c r="WCX25" s="21"/>
+      <c r="WDB25" s="21"/>
+      <c r="WDF25" s="21"/>
+      <c r="WDJ25" s="21"/>
+      <c r="WDN25" s="21"/>
+      <c r="WDR25" s="21"/>
+      <c r="WDV25" s="21"/>
+      <c r="WDZ25" s="21"/>
+      <c r="WED25" s="21"/>
+      <c r="WEH25" s="21"/>
+      <c r="WEL25" s="21"/>
+      <c r="WEP25" s="21"/>
+      <c r="WET25" s="21"/>
+      <c r="WEX25" s="21"/>
+      <c r="WFB25" s="21"/>
+      <c r="WFF25" s="21"/>
+      <c r="WFJ25" s="21"/>
+      <c r="WFN25" s="21"/>
+      <c r="WFR25" s="21"/>
+      <c r="WFV25" s="21"/>
+      <c r="WFZ25" s="21"/>
+      <c r="WGD25" s="21"/>
+      <c r="WGH25" s="21"/>
+      <c r="WGL25" s="21"/>
+      <c r="WGP25" s="21"/>
+      <c r="WGT25" s="21"/>
+      <c r="WGX25" s="21"/>
+      <c r="WHB25" s="21"/>
+      <c r="WHF25" s="21"/>
+      <c r="WHJ25" s="21"/>
+      <c r="WHN25" s="21"/>
+      <c r="WHR25" s="21"/>
+      <c r="WHV25" s="21"/>
+      <c r="WHZ25" s="21"/>
+      <c r="WID25" s="21"/>
+      <c r="WIH25" s="21"/>
+      <c r="WIL25" s="21"/>
+      <c r="WIP25" s="21"/>
+      <c r="WIT25" s="21"/>
+      <c r="WIX25" s="21"/>
+      <c r="WJB25" s="21"/>
+      <c r="WJF25" s="21"/>
+      <c r="WJJ25" s="21"/>
+      <c r="WJN25" s="21"/>
+      <c r="WJR25" s="21"/>
+      <c r="WJV25" s="21"/>
+      <c r="WJZ25" s="21"/>
+      <c r="WKD25" s="21"/>
+      <c r="WKH25" s="21"/>
+      <c r="WKL25" s="21"/>
+      <c r="WKP25" s="21"/>
+      <c r="WKT25" s="21"/>
+      <c r="WKX25" s="21"/>
+      <c r="WLB25" s="21"/>
+      <c r="WLF25" s="21"/>
+      <c r="WLJ25" s="21"/>
+      <c r="WLN25" s="21"/>
+      <c r="WLR25" s="21"/>
+      <c r="WLV25" s="21"/>
+      <c r="WLZ25" s="21"/>
+      <c r="WMD25" s="21"/>
+      <c r="WMH25" s="21"/>
+      <c r="WML25" s="21"/>
+      <c r="WMP25" s="21"/>
+      <c r="WMT25" s="21"/>
+      <c r="WMX25" s="21"/>
+      <c r="WNB25" s="21"/>
+      <c r="WNF25" s="21"/>
+      <c r="WNJ25" s="21"/>
+      <c r="WNN25" s="21"/>
+      <c r="WNR25" s="21"/>
+      <c r="WNV25" s="21"/>
+      <c r="WNZ25" s="21"/>
+      <c r="WOD25" s="21"/>
+      <c r="WOH25" s="21"/>
+      <c r="WOL25" s="21"/>
+      <c r="WOP25" s="21"/>
+      <c r="WOT25" s="21"/>
+      <c r="WOX25" s="21"/>
+      <c r="WPB25" s="21"/>
+      <c r="WPF25" s="21"/>
+      <c r="WPJ25" s="21"/>
+      <c r="WPN25" s="21"/>
+      <c r="WPR25" s="21"/>
+      <c r="WPV25" s="21"/>
+      <c r="WPZ25" s="21"/>
+      <c r="WQD25" s="21"/>
+      <c r="WQH25" s="21"/>
+      <c r="WQL25" s="21"/>
+      <c r="WQP25" s="21"/>
+      <c r="WQT25" s="21"/>
+      <c r="WQX25" s="21"/>
+      <c r="WRB25" s="21"/>
+      <c r="WRF25" s="21"/>
+      <c r="WRJ25" s="21"/>
+      <c r="WRN25" s="21"/>
+      <c r="WRR25" s="21"/>
+      <c r="WRV25" s="21"/>
+      <c r="WRZ25" s="21"/>
+      <c r="WSD25" s="21"/>
+      <c r="WSH25" s="21"/>
+      <c r="WSL25" s="21"/>
+      <c r="WSP25" s="21"/>
+      <c r="WST25" s="21"/>
+      <c r="WSX25" s="21"/>
+      <c r="WTB25" s="21"/>
+      <c r="WTF25" s="21"/>
+      <c r="WTJ25" s="21"/>
+      <c r="WTN25" s="21"/>
+      <c r="WTR25" s="21"/>
+      <c r="WTV25" s="21"/>
+      <c r="WTZ25" s="21"/>
+      <c r="WUD25" s="21"/>
+      <c r="WUH25" s="21"/>
+      <c r="WUL25" s="21"/>
+      <c r="WUP25" s="21"/>
+      <c r="WUT25" s="21"/>
+      <c r="WUX25" s="21"/>
+      <c r="WVB25" s="21"/>
+      <c r="WVF25" s="21"/>
+      <c r="WVJ25" s="21"/>
+      <c r="WVN25" s="21"/>
+      <c r="WVR25" s="21"/>
+      <c r="WVV25" s="21"/>
+      <c r="WVZ25" s="21"/>
+      <c r="WWD25" s="21"/>
+      <c r="WWH25" s="21"/>
+      <c r="WWL25" s="21"/>
+      <c r="WWP25" s="21"/>
+      <c r="WWT25" s="21"/>
+      <c r="WWX25" s="21"/>
+      <c r="WXB25" s="21"/>
+      <c r="WXF25" s="21"/>
+      <c r="WXJ25" s="21"/>
+      <c r="WXN25" s="21"/>
+      <c r="WXR25" s="21"/>
+      <c r="WXV25" s="21"/>
+      <c r="WXZ25" s="21"/>
+      <c r="WYD25" s="21"/>
+      <c r="WYH25" s="21"/>
+      <c r="WYL25" s="21"/>
+      <c r="WYP25" s="21"/>
+      <c r="WYT25" s="21"/>
+      <c r="WYX25" s="21"/>
+      <c r="WZB25" s="21"/>
+      <c r="WZF25" s="21"/>
+      <c r="WZJ25" s="21"/>
+      <c r="WZN25" s="21"/>
+      <c r="WZR25" s="21"/>
+      <c r="WZV25" s="21"/>
+      <c r="WZZ25" s="21"/>
+      <c r="XAD25" s="21"/>
+      <c r="XAH25" s="21"/>
+      <c r="XAL25" s="21"/>
+      <c r="XAP25" s="21"/>
+      <c r="XAT25" s="21"/>
+      <c r="XAX25" s="21"/>
+      <c r="XBB25" s="21"/>
+      <c r="XBF25" s="21"/>
+      <c r="XBJ25" s="21"/>
+      <c r="XBN25" s="21"/>
+      <c r="XBR25" s="21"/>
+      <c r="XBV25" s="21"/>
+      <c r="XBZ25" s="21"/>
+      <c r="XCD25" s="21"/>
+      <c r="XCH25" s="21"/>
+      <c r="XCL25" s="21"/>
+      <c r="XCP25" s="21"/>
+      <c r="XCT25" s="21"/>
+      <c r="XCX25" s="21"/>
+      <c r="XDB25" s="21"/>
+      <c r="XDF25" s="21"/>
+      <c r="XDJ25" s="21"/>
+      <c r="XDN25" s="21"/>
+      <c r="XDR25" s="21"/>
+      <c r="XDV25" s="21"/>
+      <c r="XDZ25" s="21"/>
+      <c r="XED25" s="21"/>
+      <c r="XEH25" s="21"/>
+      <c r="XEL25" s="21"/>
+      <c r="XEP25" s="21"/>
+      <c r="XET25" s="21"/>
+      <c r="XEX25" s="21"/>
+      <c r="XFB25" s="21"/>
+    </row>
+    <row r="26" spans="1:1022 1026:2046 2050:3070 3074:4094 4098:5118 5122:6142 6146:7166 7170:8190 8194:9214 9218:10238 10242:11262 11266:12286 12290:13310 13314:14334 14338:15358 15362:16382" x14ac:dyDescent="0.3">
+      <c r="A26" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B26" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="C26" s="25" t="s">
+        <v>2</v>
+      </c>
+      <c r="D26" s="25" t="s">
+        <v>60</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="F26" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="G26" s="25" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1022 1026:2046 2050:3070 3074:4094 4098:5118 5122:6142 6146:7166 7170:8190 8194:9214 9218:10238 10242:11262 11266:12286 12290:13310 13314:14334 14338:15358 15362:16382" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>1</v>
+      </c>
+      <c r="B27" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="C27" s="25" t="s">
+        <v>59</v>
+      </c>
+      <c r="D27" s="25" t="s">
+        <v>65</v>
+      </c>
+      <c r="E27" s="25" t="s">
+        <v>66</v>
+      </c>
+      <c r="F27" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="G27" s="25" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1022 1026:2046 2050:3070 3074:4094 4098:5118 5122:6142 6146:7166 7170:8190 8194:9214 9218:10238 10242:11262 11266:12286 12290:13310 13314:14334 14338:15358 15362:16382" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>1</v>
+      </c>
+      <c r="B28" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="C28" s="25" t="s">
+        <v>59</v>
+      </c>
+      <c r="D28" s="25" t="s">
+        <v>65</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="G28" s="25" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1022 1026:2046 2050:3070 3074:4094 4098:5118 5122:6142 6146:7166 7170:8190 8194:9214 9218:10238 10242:11262 11266:12286 12290:13310 13314:14334 14338:15358 15362:16382" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>0</v>
+      </c>
+      <c r="C29" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="D29" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="E29" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="F29" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="G29" s="23" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1022 1026:2046 2050:3070 3074:4094 4098:5118 5122:6142 6146:7166 7170:8190 8194:9214 9218:10238 10242:11262 11266:12286 12290:13310 13314:14334 14338:15358 15362:16382" ht="17.25" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1022 1026:2046 2050:3070 3074:4094 4098:5118 5122:6142 6146:7166 7170:8190 8194:9214 9218:10238 10242:11262 11266:12286 12290:13310 13314:14334 14338:15358 15362:16382" x14ac:dyDescent="0.3">
+      <c r="C32" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="3:7" x14ac:dyDescent="0.3">
+      <c r="C33" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F33" s="24" t="s">
+        <v>48</v>
+      </c>
+      <c r="G33" s="24" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="34" spans="3:7" x14ac:dyDescent="0.3">
+      <c r="C34" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="D34" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="E34" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="F34" s="10" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="35" spans="3:7" x14ac:dyDescent="0.3">
+      <c r="C35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E35" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="F35" s="4" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="36" spans="3:7" x14ac:dyDescent="0.3">
+      <c r="C36" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E36" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F36" s="4" t="s">
+        <v>38</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/투자관련_개발현황_20250601.xlsx
+++ b/투자관련_개발현황_20250601.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/409b82bc37418700/바탕 화면/investment/investment_strategy/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="104" documentId="13_ncr:1_{F81ACB94-9D9E-4D70-8436-AA565A3160B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A8C7156C-FCBB-4647-B2B2-828650FF50F6}"/>
+  <xr:revisionPtr revIDLastSave="163" documentId="13_ncr:1_{F81ACB94-9D9E-4D70-8436-AA565A3160B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7FA02E43-43E5-4E15-B804-CA43B0693CB7}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="29940" windowHeight="23400" activeTab="2" xr2:uid="{2C5A105A-917D-4FDB-B541-D72FFAFAEB11}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="29940" windowHeight="23400" activeTab="3" xr2:uid="{2C5A105A-917D-4FDB-B541-D72FFAFAEB11}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
     <sheet name="2026_01" sheetId="3" r:id="rId3"/>
+    <sheet name="2026-01-30" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="106">
   <si>
     <t>미국주식</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -351,6 +352,91 @@
   </si>
   <si>
     <t xml:space="preserve">거시경제 데이터를 수집하는 API 수집 코드가 필요하다 (미국, 한국 모두)  + 이걸 예측하는 함수와 물려야 한다 (최소 12개월 예측) </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>FMP_US_FS_DATA_API_V2.ipynb</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>미국 주식</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>미국 기업 주가</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>미국 기업 시가총액</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">미국 기업 재무제표 수집 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>미국 거시 경제지표 수집</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SEC_EDGAR</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">FMP </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>step1_collect_price_data.py</t>
+  </si>
+  <si>
+    <t xml:space="preserve">미국 기업 주가 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">날짜 조정을 통해 최신 데이터 업데이트 필요 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>FMP_대상_ticker_스크린.ipynb</t>
+  </si>
+  <si>
+    <t>대상기업선정</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>:상장후 10년 경과된 기업중 시총 2000위 종목</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>get_fs_data_from_edgar_VER3.ipynb</t>
+  </si>
+  <si>
+    <t>US_FMP_FS_DATA_API.ipynb</t>
+  </si>
+  <si>
+    <t>us_stock_daily_market_cap</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sec_financial_data</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>US_trade_data_collect.ipynb</t>
+  </si>
+  <si>
+    <t>us_import_data_downloader_fast.py</t>
+  </si>
+  <si>
+    <t>us_trade_data</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">us_trade_export_quarter_with_forecast </t>
+  </si>
+  <si>
+    <t xml:space="preserve">us_trade_export_monthly_with_forecast </t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -358,7 +444,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -371,6 +457,15 @@
       <sz val="8"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
@@ -494,7 +589,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -558,6 +653,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -573,6 +671,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1496,7 +1598,7 @@
         <v>19</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>44</v>
+        <v>83</v>
       </c>
       <c r="F11" s="10" t="s">
         <v>45</v>
@@ -6046,4 +6148,112 @@
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4CA41960-90A8-432B-8DDA-5F217B0D8A10}">
+  <dimension ref="A1:I28"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="43" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.875" customWidth="1"/>
+    <col min="5" max="5" width="42.875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="27.25" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="38.125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B3" t="s">
+        <v>95</v>
+      </c>
+      <c r="D3" t="s">
+        <v>85</v>
+      </c>
+      <c r="E3" s="21" t="s">
+        <v>91</v>
+      </c>
+      <c r="G3" s="21" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B4" t="s">
+        <v>94</v>
+      </c>
+      <c r="E4" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B5" t="s">
+        <v>96</v>
+      </c>
+      <c r="E5" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="D10" t="s">
+        <v>87</v>
+      </c>
+      <c r="E10" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="E11" s="21" t="s">
+        <v>97</v>
+      </c>
+      <c r="G11" s="21" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="E14" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="E15" s="21" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="18" spans="4:9" x14ac:dyDescent="0.3">
+      <c r="D18" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="25" spans="4:9" x14ac:dyDescent="0.3">
+      <c r="D25" t="s">
+        <v>88</v>
+      </c>
+      <c r="E25" s="21" t="s">
+        <v>101</v>
+      </c>
+      <c r="G25" s="21" t="s">
+        <v>103</v>
+      </c>
+      <c r="I25" s="21" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="26" spans="4:9" x14ac:dyDescent="0.3">
+      <c r="I26" s="21" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="28" spans="4:9" x14ac:dyDescent="0.3">
+      <c r="E28" s="21" t="s">
+        <v>102</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>